--- a/data/trainings.xlsx
+++ b/data/trainings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schaej17\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D97687-7841-4A07-BECA-B83E153962A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC75AA2-C6EC-4B9D-B7CB-1C5CAE927497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3828" yWindow="4068" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conferences" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
   <si>
     <t>date</t>
   </si>
@@ -235,6 +235,9 @@
   <si>
     <t>A critical introduction to causal mediation analysis for biostatistics</t>
   </si>
+  <si>
+    <t>Does This Treatment Cause That Outcome: A Practical Guide to Estimand Thinking</t>
+  </si>
 </sst>
 </file>
 
@@ -373,7 +376,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9525" cy="9525"/>
@@ -407,7 +410,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9525" cy="9525"/>
@@ -707,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L960"/>
+  <dimension ref="A1:L961"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" style="12" customWidth="1"/>
@@ -753,13 +756,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="str">
-        <f>"11.12.2025"</f>
-        <v>11.12.2025</v>
+        <f>"25.03.2026"</f>
+        <v>25.03.2026</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5"/>
@@ -770,13 +773,13 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="str">
-        <f>"18.11.2025"</f>
-        <v>18.11.2025</v>
+        <f>"11.12.2025"</f>
+        <v>11.12.2025</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5"/>
@@ -787,64 +790,56 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="str">
+        <f>"18.11.2025"</f>
+        <v>18.11.2025</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="str">
         <f>"17.12.2024"</f>
         <v>17.12.2024</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="G4" s="5" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="G5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="str">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="str">
         <f>"12.02.2024"</f>
         <v>12.02.2024</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="str">
-        <f>"06.12.2023"</f>
-        <v>06.12.2023</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -859,200 +854,198 @@
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="str">
+        <f>"06.12.2023"</f>
+        <v>06.12.2023</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="1">
         <v>2</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="str">
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="str">
         <f>"03.09.2023"</f>
         <v>03.09.2023</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="F8" s="1">
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="str">
+    <row r="10" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="str">
         <f>"10.02.2023"</f>
         <v>10.02.2023</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="10"/>
-      <c r="F9" s="10">
+      <c r="C10" s="4"/>
+      <c r="D10" s="10"/>
+      <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="str">
+    <row r="11" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="str">
         <f>"13.09.2022"</f>
         <v>13.09.2022</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="str">
-        <f>"29.03.2022"</f>
-        <v>29.03.2022</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5">
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="F11" s="1">
         <v>1</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>9</v>
+      <c r="H11" s="5" t="s">
+        <v>48</v>
       </c>
-      <c r="I11" t="s">
-        <v>30</v>
+      <c r="I11" s="3" t="s">
+        <v>49</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J11" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="str">
         <f>"29.03.2022"</f>
         <v>29.03.2022</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="str">
+        <f>"29.03.2022"</f>
+        <v>29.03.2022</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5">
         <v>2</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="str">
+      <c r="K13" s="17"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="str">
         <f>"21.02.2022"</f>
         <v>21.02.2022</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="str">
-        <f t="shared" ref="A14:A16" si="0">"21.02.2022"</f>
-        <v>21.02.2022</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>36</v>
@@ -1061,17 +1054,17 @@
         <v>9</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A15:A17" si="0">"21.02.2022"</f>
         <v>21.02.2022</v>
       </c>
       <c r="B15" s="4"/>
@@ -1079,7 +1072,7 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>36</v>
@@ -1088,10 +1081,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="3"/>
@@ -1106,7 +1099,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>36</v>
@@ -1115,67 +1108,69 @@
         <v>9</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="str">
-        <f>"02.02.2021"</f>
-        <v>02.02.2021</v>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>21.02.2022</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>12</v>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5">
+        <v>4</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="4">
-        <v>1</v>
+      <c r="G17" s="5" t="s">
+        <v>36</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>13</v>
+      <c r="H17" s="1" t="s">
+        <v>9</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>11</v>
+      <c r="I17" s="5" t="s">
+        <v>42</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>14</v>
+      <c r="J17" s="5" t="s">
+        <v>43</v>
       </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="17"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="str">
         <f>"02.02.2021"</f>
         <v>02.02.2021</v>
       </c>
-      <c r="B18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C18" s="4"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>15</v>
+      <c r="G18" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>16</v>
+      <c r="I18" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="str">
         <f>"02.02.2021"</f>
         <v>02.02.2021</v>
@@ -1185,49 +1180,53 @@
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="str">
-        <f>"19.08.2019"</f>
-        <v>19.08.2019</v>
+        <f>"02.02.2021"</f>
+        <v>02.02.2021</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="H20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="str">
-        <f>"01.03.2018"</f>
-        <v>01.03.2018</v>
+        <f>"19.08.2019"</f>
+        <v>19.08.2019</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="6"/>
@@ -1236,44 +1235,53 @@
         <v>1</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="str">
+        <f>"01.03.2018"</f>
+        <v>01.03.2018</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="str">
         <f>"05.06.2014"</f>
         <v>05.06.2014</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="4">
+      <c r="C23" s="4"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="4">
         <v>1</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="4"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1285,7 +1293,7 @@
       <c r="I24" s="6"/>
       <c r="J24"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1297,7 +1305,7 @@
       <c r="I25" s="6"/>
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1309,7 +1317,7 @@
       <c r="I26" s="6"/>
       <c r="J26"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1321,7 +1329,7 @@
       <c r="I27" s="6"/>
       <c r="J27"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1333,7 +1341,7 @@
       <c r="I28" s="6"/>
       <c r="J28"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1345,31 +1353,31 @@
       <c r="I29" s="6"/>
       <c r="J29"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="4"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
       <c r="F31" s="4"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1378,6 +1386,7 @@
       <c r="F32" s="4"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
       <c r="J32"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -1389,7 +1398,6 @@
       <c r="F33" s="4"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
       <c r="J33"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -1412,8 +1420,8 @@
       <c r="E35" s="6"/>
       <c r="F35" s="4"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
       <c r="J35"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -1424,7 +1432,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="4"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
+      <c r="H36" s="16"/>
       <c r="I36" s="16"/>
       <c r="J36"/>
     </row>
@@ -1435,9 +1443,9 @@
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="16"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
+      <c r="I37" s="16"/>
       <c r="J37"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -1447,8 +1455,8 @@
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38"/>
     </row>
@@ -1461,7 +1469,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="6"/>
       <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
+      <c r="I39" s="6"/>
       <c r="J39"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -1483,9 +1491,9 @@
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
       <c r="J41"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -1497,7 +1505,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="16"/>
       <c r="H42" s="6"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="6"/>
       <c r="J42"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -1507,34 +1515,34 @@
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="6"/>
       <c r="I43" s="4"/>
       <c r="J43"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
+      <c r="A44" s="6"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="4"/>
+      <c r="J44"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="1"/>
-      <c r="J45"/>
+      <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -1594,7 +1602,7 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="J50"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
@@ -1614,7 +1622,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
-      <c r="F52" s="2"/>
+      <c r="F52" s="4"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="1"/>
@@ -1646,8 +1654,8 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="2"/>
@@ -1694,8 +1702,8 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="2"/>
@@ -1706,8 +1714,8 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="2"/>
@@ -1802,8 +1810,8 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="2"/>
@@ -3169,16 +3177,16 @@
       <c r="J181" s="1"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A182" s="14"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="3"/>
+      <c r="A182" s="13"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="6"/>
+      <c r="E182" s="6"/>
+      <c r="F182" s="2"/>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
-      <c r="I182" s="3"/>
-      <c r="J182" s="3"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="14"/>
@@ -12516,6 +12524,18 @@
       <c r="I960" s="3"/>
       <c r="J960" s="3"/>
     </row>
+    <row r="961" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A961" s="14"/>
+      <c r="B961" s="9"/>
+      <c r="C961" s="9"/>
+      <c r="D961" s="5"/>
+      <c r="E961" s="5"/>
+      <c r="F961" s="3"/>
+      <c r="G961" s="5"/>
+      <c r="H961" s="5"/>
+      <c r="I961" s="3"/>
+      <c r="J961" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/trainings.xlsx
+++ b/data/trainings.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schaej17\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\BBS\home\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC75AA2-C6EC-4B9D-B7CB-1C5CAE927497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046AD7EA-9233-405C-8624-CFEA2CF7083C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conferences" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
   <si>
     <t>date</t>
   </si>
@@ -238,15 +238,28 @@
   <si>
     <t>Does This Treatment Cause That Outcome: A Practical Guide to Estimand Thinking</t>
   </si>
+  <si>
+    <t>Data Monitoring Committees</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Tim Friede, David Lawrence, Tobias Mütze, Olympia Papachristofi, Marisa Bacchi</t>
+  </si>
+  <si>
+    <t>University Medical Center Göttingen, Novartis, Novartis, Novartis, AlfaSigma</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd&quot;.&quot;mm&quot;.&quot;yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -276,6 +289,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -298,7 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -352,6 +372,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -376,7 +402,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9525" cy="9525"/>
@@ -410,7 +436,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9525" cy="9525"/>
@@ -710,21 +736,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L961"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L962"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" style="12" customWidth="1"/>
-    <col min="2" max="3" width="35.21875" style="10" customWidth="1"/>
-    <col min="4" max="5" width="40.77734375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.77734375" style="12" customWidth="1"/>
-    <col min="8" max="8" width="38.5546875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="118.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27" style="12" customWidth="1"/>
+    <col min="2" max="3" width="35.28515625" style="10" customWidth="1"/>
+    <col min="4" max="5" width="40.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" style="12" customWidth="1"/>
+    <col min="8" max="8" width="38.5703125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="118.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="39" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="14.44140625" style="10"/>
+    <col min="11" max="16384" width="14.42578125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -756,30 +782,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="20" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="str">
+        <f>"26.10.2026"</f>
+        <v>26.10.2026</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="str">
         <f>"25.03.2026"</f>
         <v>25.03.2026</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="str">
-        <f>"11.12.2025"</f>
-        <v>11.12.2025</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5"/>
@@ -790,13 +817,13 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="str">
-        <f>"18.11.2025"</f>
-        <v>18.11.2025</v>
+        <f>"11.12.2025"</f>
+        <v>11.12.2025</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
@@ -807,67 +834,59 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="str">
+        <f>"18.11.2025"</f>
+        <v>18.11.2025</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="str">
         <f>"17.12.2024"</f>
         <v>17.12.2024</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="G5" s="5" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="G6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="str">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="str">
         <f>"12.02.2024"</f>
         <v>12.02.2024</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="str">
-        <f>"06.12.2023"</f>
-        <v>06.12.2023</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="str">
         <f>"06.12.2023"</f>
         <v>06.12.2023</v>
@@ -879,200 +898,198 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="str">
+        <f>"06.12.2023"</f>
+        <v>06.12.2023</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="str">
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" ht="57" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="str">
         <f>"03.09.2023"</f>
         <v>03.09.2023</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="F9" s="1">
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="str">
+    <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="str">
         <f>"10.02.2023"</f>
         <v>10.02.2023</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="10"/>
-      <c r="F10" s="10">
+      <c r="C11" s="4"/>
+      <c r="D11" s="10"/>
+      <c r="F11" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="str">
+    <row r="12" spans="1:12" ht="57" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="str">
         <f>"13.09.2022"</f>
         <v>13.09.2022</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="F11" s="1">
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="str">
-        <f>"29.03.2022"</f>
-        <v>29.03.2022</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="str">
         <f>"29.03.2022"</f>
         <v>29.03.2022</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>33</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="5"/>
       <c r="K13" s="17"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="str">
-        <f>"21.02.2022"</f>
-        <v>21.02.2022</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>35</v>
-      </c>
+        <f>"29.03.2022"</f>
+        <v>29.03.2022</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="str">
-        <f t="shared" ref="A15:A17" si="0">"21.02.2022"</f>
+        <f>"21.02.2022"</f>
         <v>21.02.2022</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>36</v>
@@ -1081,17 +1098,17 @@
         <v>9</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A16:A18" si="0">"21.02.2022"</f>
         <v>21.02.2022</v>
       </c>
       <c r="B16" s="4"/>
@@ -1099,7 +1116,7 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>36</v>
@@ -1108,15 +1125,15 @@
         <v>9</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>21.02.2022</v>
@@ -1126,7 +1143,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>36</v>
@@ -1135,67 +1152,69 @@
         <v>9</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="str">
-        <f>"02.02.2021"</f>
-        <v>02.02.2021</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>21.02.2022</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5">
+        <v>4</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="17"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="str">
         <f>"02.02.2021"</f>
         <v>02.02.2021</v>
       </c>
-      <c r="B19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C19" s="4"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="4">
-        <v>2</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="str">
         <f>"02.02.2021"</f>
         <v>02.02.2021</v>
@@ -1205,49 +1224,53 @@
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="str">
-        <f>"19.08.2019"</f>
-        <v>19.08.2019</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>22</v>
-      </c>
+        <f>"02.02.2021"</f>
+        <v>02.02.2021</v>
+      </c>
+      <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="str">
-        <f>"01.03.2018"</f>
-        <v>01.03.2018</v>
+        <f>"19.08.2019"</f>
+        <v>19.08.2019</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="6"/>
@@ -1256,44 +1279,53 @@
         <v>1</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="57" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="str">
+        <f>"01.03.2018"</f>
+        <v>01.03.2018</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="str">
         <f>"05.06.2014"</f>
         <v>05.06.2014</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="4">
+      <c r="C24" s="4"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="4">
         <v>1</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="4"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1305,7 +1337,7 @@
       <c r="I25" s="6"/>
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1317,7 +1349,7 @@
       <c r="I26" s="6"/>
       <c r="J26"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1329,7 +1361,7 @@
       <c r="I27" s="6"/>
       <c r="J27"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1341,7 +1373,7 @@
       <c r="I28" s="6"/>
       <c r="J28"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1353,7 +1385,7 @@
       <c r="I29" s="6"/>
       <c r="J29"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1365,31 +1397,31 @@
       <c r="I30" s="6"/>
       <c r="J30"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="4"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
       <c r="F32" s="4"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1398,9 +1430,10 @@
       <c r="F33" s="4"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
       <c r="J33"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1409,10 +1442,9 @@
       <c r="F34" s="4"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
       <c r="J34"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1424,7 +1456,7 @@
       <c r="I35" s="6"/>
       <c r="J35"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1432,11 +1464,11 @@
       <c r="E36" s="6"/>
       <c r="F36" s="4"/>
       <c r="G36" s="6"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
       <c r="J36"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1444,35 +1476,35 @@
       <c r="E37" s="6"/>
       <c r="F37" s="4"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="H37" s="16"/>
       <c r="I37" s="16"/>
       <c r="J37"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="16"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
+      <c r="I38" s="16"/>
       <c r="J38"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1481,10 +1513,10 @@
       <c r="F40" s="4"/>
       <c r="G40" s="6"/>
       <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
+      <c r="I40" s="6"/>
       <c r="J40"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1496,19 +1528,19 @@
       <c r="I41" s="16"/>
       <c r="J41"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
       <c r="J42"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1517,46 +1549,46 @@
       <c r="F43" s="4"/>
       <c r="G43" s="16"/>
       <c r="H43" s="6"/>
-      <c r="I43" s="4"/>
+      <c r="I43" s="6"/>
       <c r="J43"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="6"/>
       <c r="I44" s="4"/>
       <c r="J44"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G45" s="6"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="4"/>
+      <c r="J45"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="4"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="1"/>
-      <c r="J46"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -1568,7 +1600,7 @@
       <c r="I47" s="1"/>
       <c r="J47"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -1580,7 +1612,7 @@
       <c r="I48" s="1"/>
       <c r="J48"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -1592,7 +1624,7 @@
       <c r="I49" s="1"/>
       <c r="J49"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -1604,7 +1636,7 @@
       <c r="I50" s="1"/>
       <c r="J50"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -1614,9 +1646,9 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J51"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -1628,19 +1660,19 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
-      <c r="F53" s="2"/>
+      <c r="F53" s="4"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -1652,7 +1684,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="13"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -1664,10 +1696,10 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="2"/>
@@ -1676,7 +1708,7 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
@@ -1688,7 +1720,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="13"/>
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
@@ -1700,7 +1732,7 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
@@ -1712,10 +1744,10 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="2"/>
@@ -1724,10 +1756,10 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="2"/>
@@ -1736,7 +1768,7 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="13"/>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -1748,7 +1780,7 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="13"/>
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
@@ -1760,7 +1792,7 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="13"/>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
@@ -1772,7 +1804,7 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="13"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
@@ -1784,7 +1816,7 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="13"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
@@ -1796,7 +1828,7 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="13"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
@@ -1808,7 +1840,7 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="13"/>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
@@ -1820,10 +1852,10 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="13"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="2"/>
@@ -1832,7 +1864,7 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="13"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -1844,7 +1876,7 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="13"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -1856,7 +1888,7 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="13"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -1868,7 +1900,7 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="13"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -1880,7 +1912,7 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="13"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -1892,7 +1924,7 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="13"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -1904,7 +1936,7 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="13"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -1916,7 +1948,7 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="13"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -1928,7 +1960,7 @@
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="13"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -1940,7 +1972,7 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -1952,7 +1984,7 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -1964,7 +1996,7 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -1976,7 +2008,7 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -1988,7 +2020,7 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -2000,7 +2032,7 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -2012,7 +2044,7 @@
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -2024,7 +2056,7 @@
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -2036,7 +2068,7 @@
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="13"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -2048,7 +2080,7 @@
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="13"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -2060,7 +2092,7 @@
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="13"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -2072,7 +2104,7 @@
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -2084,7 +2116,7 @@
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="13"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -2096,7 +2128,7 @@
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="13"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -2108,7 +2140,7 @@
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="13"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -2120,7 +2152,7 @@
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="13"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -2132,7 +2164,7 @@
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="13"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -2144,7 +2176,7 @@
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -2156,7 +2188,7 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -2168,7 +2200,7 @@
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -2180,7 +2212,7 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -2192,7 +2224,7 @@
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -2204,7 +2236,7 @@
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -2216,7 +2248,7 @@
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -2228,7 +2260,7 @@
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -2240,7 +2272,7 @@
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -2252,7 +2284,7 @@
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -2264,7 +2296,7 @@
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="13"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -2276,7 +2308,7 @@
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="13"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -2288,7 +2320,7 @@
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -2300,7 +2332,7 @@
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="13"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -2312,7 +2344,7 @@
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="13"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -2324,7 +2356,7 @@
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="13"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -2336,7 +2368,7 @@
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="13"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -2348,7 +2380,7 @@
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="13"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
@@ -2360,7 +2392,7 @@
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
@@ -2372,7 +2404,7 @@
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="13"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
@@ -2384,7 +2416,7 @@
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="13"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
@@ -2396,7 +2428,7 @@
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
@@ -2408,7 +2440,7 @@
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
@@ -2420,7 +2452,7 @@
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
@@ -2432,7 +2464,7 @@
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
@@ -2444,7 +2476,7 @@
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -2456,7 +2488,7 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -2468,7 +2500,7 @@
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="13"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
@@ -2480,7 +2512,7 @@
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="13"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
@@ -2492,7 +2524,7 @@
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="13"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -2504,7 +2536,7 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="13"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
@@ -2516,7 +2548,7 @@
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="13"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
@@ -2528,7 +2560,7 @@
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="13"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
@@ -2540,7 +2572,7 @@
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="13"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
@@ -2552,7 +2584,7 @@
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="13"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
@@ -2564,7 +2596,7 @@
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="13"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
@@ -2576,7 +2608,7 @@
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="13"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -2588,7 +2620,7 @@
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="13"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -2600,7 +2632,7 @@
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="13"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -2612,7 +2644,7 @@
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="13"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -2624,7 +2656,7 @@
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="13"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2636,7 +2668,7 @@
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="13"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -2648,7 +2680,7 @@
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="13"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -2660,7 +2692,7 @@
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="13"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
@@ -2672,7 +2704,7 @@
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="13"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
@@ -2684,7 +2716,7 @@
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="13"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
@@ -2696,7 +2728,7 @@
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="13"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
@@ -2708,7 +2740,7 @@
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="13"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
@@ -2720,7 +2752,7 @@
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="13"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
@@ -2732,7 +2764,7 @@
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="13"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
@@ -2744,7 +2776,7 @@
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="13"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
@@ -2756,7 +2788,7 @@
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="13"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -2768,7 +2800,7 @@
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="13"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
@@ -2780,7 +2812,7 @@
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="13"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -2792,7 +2824,7 @@
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="13"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -2804,7 +2836,7 @@
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -2816,7 +2848,7 @@
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -2828,7 +2860,7 @@
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -2840,7 +2872,7 @@
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -2852,7 +2884,7 @@
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -2864,7 +2896,7 @@
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -2876,7 +2908,7 @@
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -2888,7 +2920,7 @@
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -2900,7 +2932,7 @@
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="13"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -2912,7 +2944,7 @@
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="13"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -2924,7 +2956,7 @@
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="13"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -2936,7 +2968,7 @@
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="13"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -2948,7 +2980,7 @@
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="13"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -2960,7 +2992,7 @@
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="13"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -2972,7 +3004,7 @@
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="13"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
@@ -2984,7 +3016,7 @@
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="13"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
@@ -2996,7 +3028,7 @@
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="13"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
@@ -3008,7 +3040,7 @@
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="13"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
@@ -3020,7 +3052,7 @@
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="13"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
@@ -3032,7 +3064,7 @@
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="13"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
@@ -3044,7 +3076,7 @@
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="13"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
@@ -3056,7 +3088,7 @@
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="13"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
@@ -3068,7 +3100,7 @@
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="13"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
@@ -3080,7 +3112,7 @@
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="13"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
@@ -3092,7 +3124,7 @@
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="13"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
@@ -3104,7 +3136,7 @@
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="13"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
@@ -3116,7 +3148,7 @@
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="13"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
@@ -3128,7 +3160,7 @@
       <c r="I177" s="1"/>
       <c r="J177" s="1"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="13"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -3140,7 +3172,7 @@
       <c r="I178" s="1"/>
       <c r="J178" s="1"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
@@ -3152,7 +3184,7 @@
       <c r="I179" s="1"/>
       <c r="J179" s="1"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="13"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
@@ -3164,7 +3196,7 @@
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="13"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -3176,7 +3208,7 @@
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="13"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
@@ -3188,19 +3220,19 @@
       <c r="I182" s="1"/>
       <c r="J182" s="1"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A183" s="14"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="3"/>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="13"/>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
+      <c r="F183" s="2"/>
       <c r="G183" s="5"/>
       <c r="H183" s="5"/>
-      <c r="I183" s="3"/>
-      <c r="J183" s="3"/>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="14"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
@@ -3212,7 +3244,7 @@
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="14"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
@@ -3224,7 +3256,7 @@
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="14"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
@@ -3236,7 +3268,7 @@
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="14"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
@@ -3248,7 +3280,7 @@
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="14"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -3260,7 +3292,7 @@
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="14"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -3272,7 +3304,7 @@
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="14"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
@@ -3284,7 +3316,7 @@
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="14"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
@@ -3296,7 +3328,7 @@
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="14"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
@@ -3308,7 +3340,7 @@
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="14"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
@@ -3320,7 +3352,7 @@
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="14"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
@@ -3332,7 +3364,7 @@
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="14"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
@@ -3344,7 +3376,7 @@
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="14"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
@@ -3356,7 +3388,7 @@
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="14"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -3368,7 +3400,7 @@
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="14"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
@@ -3380,7 +3412,7 @@
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="14"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -3392,7 +3424,7 @@
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="14"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -3404,7 +3436,7 @@
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="14"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
@@ -3416,7 +3448,7 @@
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="14"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
@@ -3428,7 +3460,7 @@
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="14"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
@@ -3440,7 +3472,7 @@
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="14"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -3452,7 +3484,7 @@
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="14"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
@@ -3464,7 +3496,7 @@
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="14"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
@@ -3476,7 +3508,7 @@
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="14"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
@@ -3488,7 +3520,7 @@
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="14"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
@@ -3500,7 +3532,7 @@
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="14"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
@@ -3512,7 +3544,7 @@
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="14"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
@@ -3524,7 +3556,7 @@
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="14"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
@@ -3536,7 +3568,7 @@
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="14"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
@@ -3548,7 +3580,7 @@
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="14"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
@@ -3560,7 +3592,7 @@
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="14"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
@@ -3572,7 +3604,7 @@
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="14"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
@@ -3584,7 +3616,7 @@
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="14"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
@@ -3596,7 +3628,7 @@
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="14"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
@@ -3608,7 +3640,7 @@
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="14"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
@@ -3620,7 +3652,7 @@
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="14"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
@@ -3632,7 +3664,7 @@
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="14"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
@@ -3644,7 +3676,7 @@
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="14"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
@@ -3656,7 +3688,7 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="14"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
@@ -3668,7 +3700,7 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="14"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
@@ -3680,7 +3712,7 @@
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="14"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
@@ -3692,7 +3724,7 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="14"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
@@ -3704,7 +3736,7 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="14"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
@@ -3716,7 +3748,7 @@
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="14"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
@@ -3728,7 +3760,7 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="14"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
@@ -3740,7 +3772,7 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="14"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
@@ -3752,7 +3784,7 @@
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="14"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
@@ -3764,7 +3796,7 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="14"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
@@ -3776,7 +3808,7 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="14"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
@@ -3788,7 +3820,7 @@
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="14"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
@@ -3800,7 +3832,7 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="14"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
@@ -3812,7 +3844,7 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="14"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
@@ -3824,7 +3856,7 @@
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="14"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
@@ -3836,7 +3868,7 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="14"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
@@ -3848,7 +3880,7 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="14"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
@@ -3860,7 +3892,7 @@
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="14"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
@@ -3872,7 +3904,7 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="14"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
@@ -3884,7 +3916,7 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="14"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
@@ -3896,7 +3928,7 @@
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="14"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
@@ -3908,7 +3940,7 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="14"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
@@ -3920,7 +3952,7 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="14"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
@@ -3932,7 +3964,7 @@
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="14"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
@@ -3944,7 +3976,7 @@
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="14"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
@@ -3956,7 +3988,7 @@
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="14"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
@@ -3968,7 +4000,7 @@
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="14"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
@@ -3980,7 +4012,7 @@
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="14"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
@@ -3992,7 +4024,7 @@
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="14"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
@@ -4004,7 +4036,7 @@
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="14"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
@@ -4016,7 +4048,7 @@
       <c r="I251" s="3"/>
       <c r="J251" s="3"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="14"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
@@ -4028,7 +4060,7 @@
       <c r="I252" s="3"/>
       <c r="J252" s="3"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="14"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
@@ -4040,7 +4072,7 @@
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="14"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
@@ -4052,7 +4084,7 @@
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="14"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
@@ -4064,7 +4096,7 @@
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="14"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
@@ -4076,7 +4108,7 @@
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="14"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
@@ -4088,7 +4120,7 @@
       <c r="I257" s="3"/>
       <c r="J257" s="3"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="14"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
@@ -4100,7 +4132,7 @@
       <c r="I258" s="3"/>
       <c r="J258" s="3"/>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="14"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
@@ -4112,7 +4144,7 @@
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="14"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
@@ -4124,7 +4156,7 @@
       <c r="I260" s="3"/>
       <c r="J260" s="3"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="14"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
@@ -4136,7 +4168,7 @@
       <c r="I261" s="3"/>
       <c r="J261" s="3"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="14"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
@@ -4148,7 +4180,7 @@
       <c r="I262" s="3"/>
       <c r="J262" s="3"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="14"/>
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
@@ -4160,7 +4192,7 @@
       <c r="I263" s="3"/>
       <c r="J263" s="3"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="14"/>
       <c r="B264" s="9"/>
       <c r="C264" s="9"/>
@@ -4172,7 +4204,7 @@
       <c r="I264" s="3"/>
       <c r="J264" s="3"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="14"/>
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
@@ -4184,7 +4216,7 @@
       <c r="I265" s="3"/>
       <c r="J265" s="3"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="14"/>
       <c r="B266" s="9"/>
       <c r="C266" s="9"/>
@@ -4196,7 +4228,7 @@
       <c r="I266" s="3"/>
       <c r="J266" s="3"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="14"/>
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
@@ -4208,7 +4240,7 @@
       <c r="I267" s="3"/>
       <c r="J267" s="3"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="14"/>
       <c r="B268" s="9"/>
       <c r="C268" s="9"/>
@@ -4220,7 +4252,7 @@
       <c r="I268" s="3"/>
       <c r="J268" s="3"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="14"/>
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
@@ -4232,7 +4264,7 @@
       <c r="I269" s="3"/>
       <c r="J269" s="3"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="14"/>
       <c r="B270" s="9"/>
       <c r="C270" s="9"/>
@@ -4244,7 +4276,7 @@
       <c r="I270" s="3"/>
       <c r="J270" s="3"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="14"/>
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
@@ -4256,7 +4288,7 @@
       <c r="I271" s="3"/>
       <c r="J271" s="3"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="14"/>
       <c r="B272" s="9"/>
       <c r="C272" s="9"/>
@@ -4268,7 +4300,7 @@
       <c r="I272" s="3"/>
       <c r="J272" s="3"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="14"/>
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
@@ -4280,7 +4312,7 @@
       <c r="I273" s="3"/>
       <c r="J273" s="3"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="14"/>
       <c r="B274" s="9"/>
       <c r="C274" s="9"/>
@@ -4292,7 +4324,7 @@
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="14"/>
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
@@ -4304,7 +4336,7 @@
       <c r="I275" s="3"/>
       <c r="J275" s="3"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="14"/>
       <c r="B276" s="9"/>
       <c r="C276" s="9"/>
@@ -4316,7 +4348,7 @@
       <c r="I276" s="3"/>
       <c r="J276" s="3"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="14"/>
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
@@ -4328,7 +4360,7 @@
       <c r="I277" s="3"/>
       <c r="J277" s="3"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="14"/>
       <c r="B278" s="9"/>
       <c r="C278" s="9"/>
@@ -4340,7 +4372,7 @@
       <c r="I278" s="3"/>
       <c r="J278" s="3"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="14"/>
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
@@ -4352,7 +4384,7 @@
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="14"/>
       <c r="B280" s="9"/>
       <c r="C280" s="9"/>
@@ -4364,7 +4396,7 @@
       <c r="I280" s="3"/>
       <c r="J280" s="3"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="14"/>
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
@@ -4376,7 +4408,7 @@
       <c r="I281" s="3"/>
       <c r="J281" s="3"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="14"/>
       <c r="B282" s="9"/>
       <c r="C282" s="9"/>
@@ -4388,7 +4420,7 @@
       <c r="I282" s="3"/>
       <c r="J282" s="3"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="14"/>
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
@@ -4400,7 +4432,7 @@
       <c r="I283" s="3"/>
       <c r="J283" s="3"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="14"/>
       <c r="B284" s="9"/>
       <c r="C284" s="9"/>
@@ -4412,7 +4444,7 @@
       <c r="I284" s="3"/>
       <c r="J284" s="3"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="14"/>
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
@@ -4424,7 +4456,7 @@
       <c r="I285" s="3"/>
       <c r="J285" s="3"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="14"/>
       <c r="B286" s="9"/>
       <c r="C286" s="9"/>
@@ -4436,7 +4468,7 @@
       <c r="I286" s="3"/>
       <c r="J286" s="3"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="14"/>
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
@@ -4448,7 +4480,7 @@
       <c r="I287" s="3"/>
       <c r="J287" s="3"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="14"/>
       <c r="B288" s="9"/>
       <c r="C288" s="9"/>
@@ -4460,7 +4492,7 @@
       <c r="I288" s="3"/>
       <c r="J288" s="3"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="14"/>
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
@@ -4472,7 +4504,7 @@
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="14"/>
       <c r="B290" s="9"/>
       <c r="C290" s="9"/>
@@ -4484,7 +4516,7 @@
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="14"/>
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
@@ -4496,7 +4528,7 @@
       <c r="I291" s="3"/>
       <c r="J291" s="3"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="14"/>
       <c r="B292" s="9"/>
       <c r="C292" s="9"/>
@@ -4508,7 +4540,7 @@
       <c r="I292" s="3"/>
       <c r="J292" s="3"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="14"/>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
@@ -4520,7 +4552,7 @@
       <c r="I293" s="3"/>
       <c r="J293" s="3"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="14"/>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
@@ -4532,7 +4564,7 @@
       <c r="I294" s="3"/>
       <c r="J294" s="3"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="14"/>
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
@@ -4544,7 +4576,7 @@
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="14"/>
       <c r="B296" s="9"/>
       <c r="C296" s="9"/>
@@ -4556,7 +4588,7 @@
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="14"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
@@ -4568,7 +4600,7 @@
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="14"/>
       <c r="B298" s="9"/>
       <c r="C298" s="9"/>
@@ -4580,7 +4612,7 @@
       <c r="I298" s="3"/>
       <c r="J298" s="3"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="14"/>
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
@@ -4592,7 +4624,7 @@
       <c r="I299" s="3"/>
       <c r="J299" s="3"/>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="14"/>
       <c r="B300" s="9"/>
       <c r="C300" s="9"/>
@@ -4604,7 +4636,7 @@
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="14"/>
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
@@ -4616,7 +4648,7 @@
       <c r="I301" s="3"/>
       <c r="J301" s="3"/>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="14"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
@@ -4628,7 +4660,7 @@
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="14"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
@@ -4640,7 +4672,7 @@
       <c r="I303" s="3"/>
       <c r="J303" s="3"/>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="14"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
@@ -4652,7 +4684,7 @@
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="14"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
@@ -4664,7 +4696,7 @@
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="14"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
@@ -4676,7 +4708,7 @@
       <c r="I306" s="3"/>
       <c r="J306" s="3"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="14"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
@@ -4688,7 +4720,7 @@
       <c r="I307" s="3"/>
       <c r="J307" s="3"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="14"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
@@ -4700,7 +4732,7 @@
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="14"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
@@ -4712,7 +4744,7 @@
       <c r="I309" s="3"/>
       <c r="J309" s="3"/>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="14"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
@@ -4724,7 +4756,7 @@
       <c r="I310" s="3"/>
       <c r="J310" s="3"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="14"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
@@ -4736,7 +4768,7 @@
       <c r="I311" s="3"/>
       <c r="J311" s="3"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="14"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
@@ -4748,7 +4780,7 @@
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="14"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
@@ -4760,7 +4792,7 @@
       <c r="I313" s="3"/>
       <c r="J313" s="3"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="14"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
@@ -4772,7 +4804,7 @@
       <c r="I314" s="3"/>
       <c r="J314" s="3"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="14"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
@@ -4784,7 +4816,7 @@
       <c r="I315" s="3"/>
       <c r="J315" s="3"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="14"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
@@ -4796,7 +4828,7 @@
       <c r="I316" s="3"/>
       <c r="J316" s="3"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="14"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
@@ -4808,7 +4840,7 @@
       <c r="I317" s="3"/>
       <c r="J317" s="3"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="14"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
@@ -4820,7 +4852,7 @@
       <c r="I318" s="3"/>
       <c r="J318" s="3"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="14"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
@@ -4832,7 +4864,7 @@
       <c r="I319" s="3"/>
       <c r="J319" s="3"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="14"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
@@ -4844,7 +4876,7 @@
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="14"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
@@ -4856,7 +4888,7 @@
       <c r="I321" s="3"/>
       <c r="J321" s="3"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="14"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
@@ -4868,7 +4900,7 @@
       <c r="I322" s="3"/>
       <c r="J322" s="3"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="14"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
@@ -4880,7 +4912,7 @@
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="14"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
@@ -4892,7 +4924,7 @@
       <c r="I324" s="3"/>
       <c r="J324" s="3"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="14"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
@@ -4904,7 +4936,7 @@
       <c r="I325" s="3"/>
       <c r="J325" s="3"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="14"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
@@ -4916,7 +4948,7 @@
       <c r="I326" s="3"/>
       <c r="J326" s="3"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="14"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
@@ -4928,7 +4960,7 @@
       <c r="I327" s="3"/>
       <c r="J327" s="3"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="14"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
@@ -4940,7 +4972,7 @@
       <c r="I328" s="3"/>
       <c r="J328" s="3"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="14"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
@@ -4952,7 +4984,7 @@
       <c r="I329" s="3"/>
       <c r="J329" s="3"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="14"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
@@ -4964,7 +4996,7 @@
       <c r="I330" s="3"/>
       <c r="J330" s="3"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="14"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
@@ -4976,7 +5008,7 @@
       <c r="I331" s="3"/>
       <c r="J331" s="3"/>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="14"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
@@ -4988,7 +5020,7 @@
       <c r="I332" s="3"/>
       <c r="J332" s="3"/>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" s="14"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
@@ -5000,7 +5032,7 @@
       <c r="I333" s="3"/>
       <c r="J333" s="3"/>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" s="14"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
@@ -5012,7 +5044,7 @@
       <c r="I334" s="3"/>
       <c r="J334" s="3"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" s="14"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
@@ -5024,7 +5056,7 @@
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" s="14"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
@@ -5036,7 +5068,7 @@
       <c r="I336" s="3"/>
       <c r="J336" s="3"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="14"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
@@ -5048,7 +5080,7 @@
       <c r="I337" s="3"/>
       <c r="J337" s="3"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="14"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
@@ -5060,7 +5092,7 @@
       <c r="I338" s="3"/>
       <c r="J338" s="3"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="14"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
@@ -5072,7 +5104,7 @@
       <c r="I339" s="3"/>
       <c r="J339" s="3"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="14"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
@@ -5084,7 +5116,7 @@
       <c r="I340" s="3"/>
       <c r="J340" s="3"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="14"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
@@ -5096,7 +5128,7 @@
       <c r="I341" s="3"/>
       <c r="J341" s="3"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="14"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
@@ -5108,7 +5140,7 @@
       <c r="I342" s="3"/>
       <c r="J342" s="3"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="14"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
@@ -5120,7 +5152,7 @@
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="14"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
@@ -5132,7 +5164,7 @@
       <c r="I344" s="3"/>
       <c r="J344" s="3"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="14"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
@@ -5144,7 +5176,7 @@
       <c r="I345" s="3"/>
       <c r="J345" s="3"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="14"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
@@ -5156,7 +5188,7 @@
       <c r="I346" s="3"/>
       <c r="J346" s="3"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="14"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
@@ -5168,7 +5200,7 @@
       <c r="I347" s="3"/>
       <c r="J347" s="3"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="14"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
@@ -5180,7 +5212,7 @@
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" s="14"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
@@ -5192,7 +5224,7 @@
       <c r="I349" s="3"/>
       <c r="J349" s="3"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" s="14"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
@@ -5204,7 +5236,7 @@
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="14"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
@@ -5216,7 +5248,7 @@
       <c r="I351" s="3"/>
       <c r="J351" s="3"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="14"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
@@ -5228,7 +5260,7 @@
       <c r="I352" s="3"/>
       <c r="J352" s="3"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353" s="14"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
@@ -5240,7 +5272,7 @@
       <c r="I353" s="3"/>
       <c r="J353" s="3"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" s="14"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
@@ -5252,7 +5284,7 @@
       <c r="I354" s="3"/>
       <c r="J354" s="3"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" s="14"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
@@ -5264,7 +5296,7 @@
       <c r="I355" s="3"/>
       <c r="J355" s="3"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="14"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
@@ -5276,7 +5308,7 @@
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" s="14"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
@@ -5288,7 +5320,7 @@
       <c r="I357" s="3"/>
       <c r="J357" s="3"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="14"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
@@ -5300,7 +5332,7 @@
       <c r="I358" s="3"/>
       <c r="J358" s="3"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" s="14"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
@@ -5312,7 +5344,7 @@
       <c r="I359" s="3"/>
       <c r="J359" s="3"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" s="14"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
@@ -5324,7 +5356,7 @@
       <c r="I360" s="3"/>
       <c r="J360" s="3"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361" s="14"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
@@ -5336,7 +5368,7 @@
       <c r="I361" s="3"/>
       <c r="J361" s="3"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" s="14"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
@@ -5348,7 +5380,7 @@
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" s="14"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
@@ -5360,7 +5392,7 @@
       <c r="I363" s="3"/>
       <c r="J363" s="3"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" s="14"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
@@ -5372,7 +5404,7 @@
       <c r="I364" s="3"/>
       <c r="J364" s="3"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" s="14"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
@@ -5384,7 +5416,7 @@
       <c r="I365" s="3"/>
       <c r="J365" s="3"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" s="14"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
@@ -5396,7 +5428,7 @@
       <c r="I366" s="3"/>
       <c r="J366" s="3"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" s="14"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
@@ -5408,7 +5440,7 @@
       <c r="I367" s="3"/>
       <c r="J367" s="3"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" s="14"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
@@ -5420,7 +5452,7 @@
       <c r="I368" s="3"/>
       <c r="J368" s="3"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" s="14"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
@@ -5432,7 +5464,7 @@
       <c r="I369" s="3"/>
       <c r="J369" s="3"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" s="14"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
@@ -5444,7 +5476,7 @@
       <c r="I370" s="3"/>
       <c r="J370" s="3"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371" s="14"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
@@ -5456,7 +5488,7 @@
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372" s="14"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
@@ -5468,7 +5500,7 @@
       <c r="I372" s="3"/>
       <c r="J372" s="3"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373" s="14"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
@@ -5480,7 +5512,7 @@
       <c r="I373" s="3"/>
       <c r="J373" s="3"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374" s="14"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
@@ -5492,7 +5524,7 @@
       <c r="I374" s="3"/>
       <c r="J374" s="3"/>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375" s="14"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
@@ -5504,7 +5536,7 @@
       <c r="I375" s="3"/>
       <c r="J375" s="3"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" s="14"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
@@ -5516,7 +5548,7 @@
       <c r="I376" s="3"/>
       <c r="J376" s="3"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377" s="14"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
@@ -5528,7 +5560,7 @@
       <c r="I377" s="3"/>
       <c r="J377" s="3"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378" s="14"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
@@ -5540,7 +5572,7 @@
       <c r="I378" s="3"/>
       <c r="J378" s="3"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" s="14"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
@@ -5552,7 +5584,7 @@
       <c r="I379" s="3"/>
       <c r="J379" s="3"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" s="14"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
@@ -5564,7 +5596,7 @@
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" s="14"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
@@ -5576,7 +5608,7 @@
       <c r="I381" s="3"/>
       <c r="J381" s="3"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382" s="14"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
@@ -5588,7 +5620,7 @@
       <c r="I382" s="3"/>
       <c r="J382" s="3"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383" s="14"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
@@ -5600,7 +5632,7 @@
       <c r="I383" s="3"/>
       <c r="J383" s="3"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384" s="14"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
@@ -5612,7 +5644,7 @@
       <c r="I384" s="3"/>
       <c r="J384" s="3"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385" s="14"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
@@ -5624,7 +5656,7 @@
       <c r="I385" s="3"/>
       <c r="J385" s="3"/>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" s="14"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
@@ -5636,7 +5668,7 @@
       <c r="I386" s="3"/>
       <c r="J386" s="3"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" s="14"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
@@ -5648,7 +5680,7 @@
       <c r="I387" s="3"/>
       <c r="J387" s="3"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" s="14"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
@@ -5660,7 +5692,7 @@
       <c r="I388" s="3"/>
       <c r="J388" s="3"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389" s="14"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
@@ -5672,7 +5704,7 @@
       <c r="I389" s="3"/>
       <c r="J389" s="3"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390" s="14"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -5684,7 +5716,7 @@
       <c r="I390" s="3"/>
       <c r="J390" s="3"/>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391" s="14"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
@@ -5696,7 +5728,7 @@
       <c r="I391" s="3"/>
       <c r="J391" s="3"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392" s="14"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
@@ -5708,7 +5740,7 @@
       <c r="I392" s="3"/>
       <c r="J392" s="3"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393" s="14"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
@@ -5720,7 +5752,7 @@
       <c r="I393" s="3"/>
       <c r="J393" s="3"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394" s="14"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
@@ -5732,7 +5764,7 @@
       <c r="I394" s="3"/>
       <c r="J394" s="3"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395" s="14"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
@@ -5744,7 +5776,7 @@
       <c r="I395" s="3"/>
       <c r="J395" s="3"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396" s="14"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
@@ -5756,7 +5788,7 @@
       <c r="I396" s="3"/>
       <c r="J396" s="3"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397" s="14"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
@@ -5768,7 +5800,7 @@
       <c r="I397" s="3"/>
       <c r="J397" s="3"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398" s="14"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
@@ -5780,7 +5812,7 @@
       <c r="I398" s="3"/>
       <c r="J398" s="3"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" s="14"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
@@ -5792,7 +5824,7 @@
       <c r="I399" s="3"/>
       <c r="J399" s="3"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" s="14"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
@@ -5804,7 +5836,7 @@
       <c r="I400" s="3"/>
       <c r="J400" s="3"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" s="14"/>
       <c r="B401" s="9"/>
       <c r="C401" s="9"/>
@@ -5816,7 +5848,7 @@
       <c r="I401" s="3"/>
       <c r="J401" s="3"/>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" s="14"/>
       <c r="B402" s="9"/>
       <c r="C402" s="9"/>
@@ -5828,7 +5860,7 @@
       <c r="I402" s="3"/>
       <c r="J402" s="3"/>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" s="14"/>
       <c r="B403" s="9"/>
       <c r="C403" s="9"/>
@@ -5840,7 +5872,7 @@
       <c r="I403" s="3"/>
       <c r="J403" s="3"/>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" s="14"/>
       <c r="B404" s="9"/>
       <c r="C404" s="9"/>
@@ -5852,7 +5884,7 @@
       <c r="I404" s="3"/>
       <c r="J404" s="3"/>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" s="14"/>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
@@ -5864,7 +5896,7 @@
       <c r="I405" s="3"/>
       <c r="J405" s="3"/>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406" s="14"/>
       <c r="B406" s="9"/>
       <c r="C406" s="9"/>
@@ -5876,7 +5908,7 @@
       <c r="I406" s="3"/>
       <c r="J406" s="3"/>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407" s="14"/>
       <c r="B407" s="9"/>
       <c r="C407" s="9"/>
@@ -5888,7 +5920,7 @@
       <c r="I407" s="3"/>
       <c r="J407" s="3"/>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408" s="14"/>
       <c r="B408" s="9"/>
       <c r="C408" s="9"/>
@@ -5900,7 +5932,7 @@
       <c r="I408" s="3"/>
       <c r="J408" s="3"/>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409" s="14"/>
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
@@ -5912,7 +5944,7 @@
       <c r="I409" s="3"/>
       <c r="J409" s="3"/>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410" s="14"/>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
@@ -5924,7 +5956,7 @@
       <c r="I410" s="3"/>
       <c r="J410" s="3"/>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411" s="14"/>
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
@@ -5936,7 +5968,7 @@
       <c r="I411" s="3"/>
       <c r="J411" s="3"/>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412" s="14"/>
       <c r="B412" s="9"/>
       <c r="C412" s="9"/>
@@ -5948,7 +5980,7 @@
       <c r="I412" s="3"/>
       <c r="J412" s="3"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413" s="14"/>
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
@@ -5960,7 +5992,7 @@
       <c r="I413" s="3"/>
       <c r="J413" s="3"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" s="14"/>
       <c r="B414" s="9"/>
       <c r="C414" s="9"/>
@@ -5972,7 +6004,7 @@
       <c r="I414" s="3"/>
       <c r="J414" s="3"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" s="14"/>
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
@@ -5984,7 +6016,7 @@
       <c r="I415" s="3"/>
       <c r="J415" s="3"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" s="14"/>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
@@ -5996,7 +6028,7 @@
       <c r="I416" s="3"/>
       <c r="J416" s="3"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" s="14"/>
       <c r="B417" s="9"/>
       <c r="C417" s="9"/>
@@ -6008,7 +6040,7 @@
       <c r="I417" s="3"/>
       <c r="J417" s="3"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418" s="14"/>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
@@ -6020,7 +6052,7 @@
       <c r="I418" s="3"/>
       <c r="J418" s="3"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" s="14"/>
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
@@ -6032,7 +6064,7 @@
       <c r="I419" s="3"/>
       <c r="J419" s="3"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" s="14"/>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
@@ -6044,7 +6076,7 @@
       <c r="I420" s="3"/>
       <c r="J420" s="3"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421" s="14"/>
       <c r="B421" s="9"/>
       <c r="C421" s="9"/>
@@ -6056,7 +6088,7 @@
       <c r="I421" s="3"/>
       <c r="J421" s="3"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422" s="14"/>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
@@ -6068,7 +6100,7 @@
       <c r="I422" s="3"/>
       <c r="J422" s="3"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423" s="14"/>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
@@ -6080,7 +6112,7 @@
       <c r="I423" s="3"/>
       <c r="J423" s="3"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" s="14"/>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -6092,7 +6124,7 @@
       <c r="I424" s="3"/>
       <c r="J424" s="3"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425" s="14"/>
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
@@ -6104,7 +6136,7 @@
       <c r="I425" s="3"/>
       <c r="J425" s="3"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" s="14"/>
       <c r="B426" s="9"/>
       <c r="C426" s="9"/>
@@ -6116,7 +6148,7 @@
       <c r="I426" s="3"/>
       <c r="J426" s="3"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427" s="14"/>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
@@ -6128,7 +6160,7 @@
       <c r="I427" s="3"/>
       <c r="J427" s="3"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428" s="14"/>
       <c r="B428" s="9"/>
       <c r="C428" s="9"/>
@@ -6140,7 +6172,7 @@
       <c r="I428" s="3"/>
       <c r="J428" s="3"/>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" s="14"/>
       <c r="B429" s="9"/>
       <c r="C429" s="9"/>
@@ -6152,7 +6184,7 @@
       <c r="I429" s="3"/>
       <c r="J429" s="3"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430" s="14"/>
       <c r="B430" s="9"/>
       <c r="C430" s="9"/>
@@ -6164,7 +6196,7 @@
       <c r="I430" s="3"/>
       <c r="J430" s="3"/>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431" s="14"/>
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
@@ -6176,7 +6208,7 @@
       <c r="I431" s="3"/>
       <c r="J431" s="3"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" s="14"/>
       <c r="B432" s="9"/>
       <c r="C432" s="9"/>
@@ -6188,7 +6220,7 @@
       <c r="I432" s="3"/>
       <c r="J432" s="3"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433" s="14"/>
       <c r="B433" s="9"/>
       <c r="C433" s="9"/>
@@ -6200,7 +6232,7 @@
       <c r="I433" s="3"/>
       <c r="J433" s="3"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434" s="14"/>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
@@ -6212,7 +6244,7 @@
       <c r="I434" s="3"/>
       <c r="J434" s="3"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435" s="14"/>
       <c r="B435" s="9"/>
       <c r="C435" s="9"/>
@@ -6224,7 +6256,7 @@
       <c r="I435" s="3"/>
       <c r="J435" s="3"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436" s="14"/>
       <c r="B436" s="9"/>
       <c r="C436" s="9"/>
@@ -6236,7 +6268,7 @@
       <c r="I436" s="3"/>
       <c r="J436" s="3"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437" s="14"/>
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
@@ -6248,7 +6280,7 @@
       <c r="I437" s="3"/>
       <c r="J437" s="3"/>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438" s="14"/>
       <c r="B438" s="9"/>
       <c r="C438" s="9"/>
@@ -6260,7 +6292,7 @@
       <c r="I438" s="3"/>
       <c r="J438" s="3"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" s="14"/>
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
@@ -6272,7 +6304,7 @@
       <c r="I439" s="3"/>
       <c r="J439" s="3"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" s="14"/>
       <c r="B440" s="9"/>
       <c r="C440" s="9"/>
@@ -6284,7 +6316,7 @@
       <c r="I440" s="3"/>
       <c r="J440" s="3"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441" s="14"/>
       <c r="B441" s="9"/>
       <c r="C441" s="9"/>
@@ -6296,7 +6328,7 @@
       <c r="I441" s="3"/>
       <c r="J441" s="3"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442" s="14"/>
       <c r="B442" s="9"/>
       <c r="C442" s="9"/>
@@ -6308,7 +6340,7 @@
       <c r="I442" s="3"/>
       <c r="J442" s="3"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443" s="14"/>
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
@@ -6320,7 +6352,7 @@
       <c r="I443" s="3"/>
       <c r="J443" s="3"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444" s="14"/>
       <c r="B444" s="9"/>
       <c r="C444" s="9"/>
@@ -6332,7 +6364,7 @@
       <c r="I444" s="3"/>
       <c r="J444" s="3"/>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445" s="14"/>
       <c r="B445" s="9"/>
       <c r="C445" s="9"/>
@@ -6344,7 +6376,7 @@
       <c r="I445" s="3"/>
       <c r="J445" s="3"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446" s="14"/>
       <c r="B446" s="9"/>
       <c r="C446" s="9"/>
@@ -6356,7 +6388,7 @@
       <c r="I446" s="3"/>
       <c r="J446" s="3"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447" s="14"/>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
@@ -6368,7 +6400,7 @@
       <c r="I447" s="3"/>
       <c r="J447" s="3"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448" s="14"/>
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
@@ -6380,7 +6412,7 @@
       <c r="I448" s="3"/>
       <c r="J448" s="3"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449" s="14"/>
       <c r="B449" s="9"/>
       <c r="C449" s="9"/>
@@ -6392,7 +6424,7 @@
       <c r="I449" s="3"/>
       <c r="J449" s="3"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450" s="14"/>
       <c r="B450" s="9"/>
       <c r="C450" s="9"/>
@@ -6404,7 +6436,7 @@
       <c r="I450" s="3"/>
       <c r="J450" s="3"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451" s="14"/>
       <c r="B451" s="9"/>
       <c r="C451" s="9"/>
@@ -6416,7 +6448,7 @@
       <c r="I451" s="3"/>
       <c r="J451" s="3"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452" s="14"/>
       <c r="B452" s="9"/>
       <c r="C452" s="9"/>
@@ -6428,7 +6460,7 @@
       <c r="I452" s="3"/>
       <c r="J452" s="3"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453" s="14"/>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -6440,7 +6472,7 @@
       <c r="I453" s="3"/>
       <c r="J453" s="3"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454" s="14"/>
       <c r="B454" s="9"/>
       <c r="C454" s="9"/>
@@ -6452,7 +6484,7 @@
       <c r="I454" s="3"/>
       <c r="J454" s="3"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455" s="14"/>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
@@ -6464,7 +6496,7 @@
       <c r="I455" s="3"/>
       <c r="J455" s="3"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456" s="14"/>
       <c r="B456" s="9"/>
       <c r="C456" s="9"/>
@@ -6476,7 +6508,7 @@
       <c r="I456" s="3"/>
       <c r="J456" s="3"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457" s="14"/>
       <c r="B457" s="9"/>
       <c r="C457" s="9"/>
@@ -6488,7 +6520,7 @@
       <c r="I457" s="3"/>
       <c r="J457" s="3"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458" s="14"/>
       <c r="B458" s="9"/>
       <c r="C458" s="9"/>
@@ -6500,7 +6532,7 @@
       <c r="I458" s="3"/>
       <c r="J458" s="3"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459" s="14"/>
       <c r="B459" s="9"/>
       <c r="C459" s="9"/>
@@ -6512,7 +6544,7 @@
       <c r="I459" s="3"/>
       <c r="J459" s="3"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460" s="14"/>
       <c r="B460" s="9"/>
       <c r="C460" s="9"/>
@@ -6524,7 +6556,7 @@
       <c r="I460" s="3"/>
       <c r="J460" s="3"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461" s="14"/>
       <c r="B461" s="9"/>
       <c r="C461" s="9"/>
@@ -6536,7 +6568,7 @@
       <c r="I461" s="3"/>
       <c r="J461" s="3"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462" s="14"/>
       <c r="B462" s="9"/>
       <c r="C462" s="9"/>
@@ -6548,7 +6580,7 @@
       <c r="I462" s="3"/>
       <c r="J462" s="3"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463" s="14"/>
       <c r="B463" s="9"/>
       <c r="C463" s="9"/>
@@ -6560,7 +6592,7 @@
       <c r="I463" s="3"/>
       <c r="J463" s="3"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464" s="14"/>
       <c r="B464" s="9"/>
       <c r="C464" s="9"/>
@@ -6572,7 +6604,7 @@
       <c r="I464" s="3"/>
       <c r="J464" s="3"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465" s="14"/>
       <c r="B465" s="9"/>
       <c r="C465" s="9"/>
@@ -6584,7 +6616,7 @@
       <c r="I465" s="3"/>
       <c r="J465" s="3"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466" s="14"/>
       <c r="B466" s="9"/>
       <c r="C466" s="9"/>
@@ -6596,7 +6628,7 @@
       <c r="I466" s="3"/>
       <c r="J466" s="3"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467" s="14"/>
       <c r="B467" s="9"/>
       <c r="C467" s="9"/>
@@ -6608,7 +6640,7 @@
       <c r="I467" s="3"/>
       <c r="J467" s="3"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468" s="14"/>
       <c r="B468" s="9"/>
       <c r="C468" s="9"/>
@@ -6620,7 +6652,7 @@
       <c r="I468" s="3"/>
       <c r="J468" s="3"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469" s="14"/>
       <c r="B469" s="9"/>
       <c r="C469" s="9"/>
@@ -6632,7 +6664,7 @@
       <c r="I469" s="3"/>
       <c r="J469" s="3"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470" s="14"/>
       <c r="B470" s="9"/>
       <c r="C470" s="9"/>
@@ -6644,7 +6676,7 @@
       <c r="I470" s="3"/>
       <c r="J470" s="3"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471" s="14"/>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
@@ -6656,7 +6688,7 @@
       <c r="I471" s="3"/>
       <c r="J471" s="3"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472" s="14"/>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
@@ -6668,7 +6700,7 @@
       <c r="I472" s="3"/>
       <c r="J472" s="3"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473" s="14"/>
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
@@ -6680,7 +6712,7 @@
       <c r="I473" s="3"/>
       <c r="J473" s="3"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474" s="14"/>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
@@ -6692,7 +6724,7 @@
       <c r="I474" s="3"/>
       <c r="J474" s="3"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475" s="14"/>
       <c r="B475" s="9"/>
       <c r="C475" s="9"/>
@@ -6704,7 +6736,7 @@
       <c r="I475" s="3"/>
       <c r="J475" s="3"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476" s="14"/>
       <c r="B476" s="9"/>
       <c r="C476" s="9"/>
@@ -6716,7 +6748,7 @@
       <c r="I476" s="3"/>
       <c r="J476" s="3"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477" s="14"/>
       <c r="B477" s="9"/>
       <c r="C477" s="9"/>
@@ -6728,7 +6760,7 @@
       <c r="I477" s="3"/>
       <c r="J477" s="3"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478" s="14"/>
       <c r="B478" s="9"/>
       <c r="C478" s="9"/>
@@ -6740,7 +6772,7 @@
       <c r="I478" s="3"/>
       <c r="J478" s="3"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479" s="14"/>
       <c r="B479" s="9"/>
       <c r="C479" s="9"/>
@@ -6752,7 +6784,7 @@
       <c r="I479" s="3"/>
       <c r="J479" s="3"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480" s="14"/>
       <c r="B480" s="9"/>
       <c r="C480" s="9"/>
@@ -6764,7 +6796,7 @@
       <c r="I480" s="3"/>
       <c r="J480" s="3"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481" s="14"/>
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
@@ -6776,7 +6808,7 @@
       <c r="I481" s="3"/>
       <c r="J481" s="3"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482" s="14"/>
       <c r="B482" s="9"/>
       <c r="C482" s="9"/>
@@ -6788,7 +6820,7 @@
       <c r="I482" s="3"/>
       <c r="J482" s="3"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483" s="14"/>
       <c r="B483" s="9"/>
       <c r="C483" s="9"/>
@@ -6800,7 +6832,7 @@
       <c r="I483" s="3"/>
       <c r="J483" s="3"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484" s="14"/>
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
@@ -6812,7 +6844,7 @@
       <c r="I484" s="3"/>
       <c r="J484" s="3"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485" s="14"/>
       <c r="B485" s="9"/>
       <c r="C485" s="9"/>
@@ -6824,7 +6856,7 @@
       <c r="I485" s="3"/>
       <c r="J485" s="3"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486" s="14"/>
       <c r="B486" s="9"/>
       <c r="C486" s="9"/>
@@ -6836,7 +6868,7 @@
       <c r="I486" s="3"/>
       <c r="J486" s="3"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487" s="14"/>
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
@@ -6848,7 +6880,7 @@
       <c r="I487" s="3"/>
       <c r="J487" s="3"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488" s="14"/>
       <c r="B488" s="9"/>
       <c r="C488" s="9"/>
@@ -6860,7 +6892,7 @@
       <c r="I488" s="3"/>
       <c r="J488" s="3"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489" s="14"/>
       <c r="B489" s="9"/>
       <c r="C489" s="9"/>
@@ -6872,7 +6904,7 @@
       <c r="I489" s="3"/>
       <c r="J489" s="3"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490" s="14"/>
       <c r="B490" s="9"/>
       <c r="C490" s="9"/>
@@ -6884,7 +6916,7 @@
       <c r="I490" s="3"/>
       <c r="J490" s="3"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491" s="14"/>
       <c r="B491" s="9"/>
       <c r="C491" s="9"/>
@@ -6896,7 +6928,7 @@
       <c r="I491" s="3"/>
       <c r="J491" s="3"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492" s="14"/>
       <c r="B492" s="9"/>
       <c r="C492" s="9"/>
@@ -6908,7 +6940,7 @@
       <c r="I492" s="3"/>
       <c r="J492" s="3"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493" s="14"/>
       <c r="B493" s="9"/>
       <c r="C493" s="9"/>
@@ -6920,7 +6952,7 @@
       <c r="I493" s="3"/>
       <c r="J493" s="3"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494" s="14"/>
       <c r="B494" s="9"/>
       <c r="C494" s="9"/>
@@ -6932,7 +6964,7 @@
       <c r="I494" s="3"/>
       <c r="J494" s="3"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495" s="14"/>
       <c r="B495" s="9"/>
       <c r="C495" s="9"/>
@@ -6944,7 +6976,7 @@
       <c r="I495" s="3"/>
       <c r="J495" s="3"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496" s="14"/>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
@@ -6956,7 +6988,7 @@
       <c r="I496" s="3"/>
       <c r="J496" s="3"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A497" s="14"/>
       <c r="B497" s="9"/>
       <c r="C497" s="9"/>
@@ -6968,7 +7000,7 @@
       <c r="I497" s="3"/>
       <c r="J497" s="3"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A498" s="14"/>
       <c r="B498" s="9"/>
       <c r="C498" s="9"/>
@@ -6980,7 +7012,7 @@
       <c r="I498" s="3"/>
       <c r="J498" s="3"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A499" s="14"/>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
@@ -6992,7 +7024,7 @@
       <c r="I499" s="3"/>
       <c r="J499" s="3"/>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A500" s="14"/>
       <c r="B500" s="9"/>
       <c r="C500" s="9"/>
@@ -7004,7 +7036,7 @@
       <c r="I500" s="3"/>
       <c r="J500" s="3"/>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A501" s="14"/>
       <c r="B501" s="9"/>
       <c r="C501" s="9"/>
@@ -7016,7 +7048,7 @@
       <c r="I501" s="3"/>
       <c r="J501" s="3"/>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A502" s="14"/>
       <c r="B502" s="9"/>
       <c r="C502" s="9"/>
@@ -7028,7 +7060,7 @@
       <c r="I502" s="3"/>
       <c r="J502" s="3"/>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A503" s="14"/>
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
@@ -7040,7 +7072,7 @@
       <c r="I503" s="3"/>
       <c r="J503" s="3"/>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A504" s="14"/>
       <c r="B504" s="9"/>
       <c r="C504" s="9"/>
@@ -7052,7 +7084,7 @@
       <c r="I504" s="3"/>
       <c r="J504" s="3"/>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A505" s="14"/>
       <c r="B505" s="9"/>
       <c r="C505" s="9"/>
@@ -7064,7 +7096,7 @@
       <c r="I505" s="3"/>
       <c r="J505" s="3"/>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A506" s="14"/>
       <c r="B506" s="9"/>
       <c r="C506" s="9"/>
@@ -7076,7 +7108,7 @@
       <c r="I506" s="3"/>
       <c r="J506" s="3"/>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A507" s="14"/>
       <c r="B507" s="9"/>
       <c r="C507" s="9"/>
@@ -7088,7 +7120,7 @@
       <c r="I507" s="3"/>
       <c r="J507" s="3"/>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A508" s="14"/>
       <c r="B508" s="9"/>
       <c r="C508" s="9"/>
@@ -7100,7 +7132,7 @@
       <c r="I508" s="3"/>
       <c r="J508" s="3"/>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A509" s="14"/>
       <c r="B509" s="9"/>
       <c r="C509" s="9"/>
@@ -7112,7 +7144,7 @@
       <c r="I509" s="3"/>
       <c r="J509" s="3"/>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A510" s="14"/>
       <c r="B510" s="9"/>
       <c r="C510" s="9"/>
@@ -7124,7 +7156,7 @@
       <c r="I510" s="3"/>
       <c r="J510" s="3"/>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A511" s="14"/>
       <c r="B511" s="9"/>
       <c r="C511" s="9"/>
@@ -7136,7 +7168,7 @@
       <c r="I511" s="3"/>
       <c r="J511" s="3"/>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A512" s="14"/>
       <c r="B512" s="9"/>
       <c r="C512" s="9"/>
@@ -7148,7 +7180,7 @@
       <c r="I512" s="3"/>
       <c r="J512" s="3"/>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513" s="14"/>
       <c r="B513" s="9"/>
       <c r="C513" s="9"/>
@@ -7160,7 +7192,7 @@
       <c r="I513" s="3"/>
       <c r="J513" s="3"/>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514" s="14"/>
       <c r="B514" s="9"/>
       <c r="C514" s="9"/>
@@ -7172,7 +7204,7 @@
       <c r="I514" s="3"/>
       <c r="J514" s="3"/>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515" s="14"/>
       <c r="B515" s="9"/>
       <c r="C515" s="9"/>
@@ -7184,7 +7216,7 @@
       <c r="I515" s="3"/>
       <c r="J515" s="3"/>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516" s="14"/>
       <c r="B516" s="9"/>
       <c r="C516" s="9"/>
@@ -7196,7 +7228,7 @@
       <c r="I516" s="3"/>
       <c r="J516" s="3"/>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517" s="14"/>
       <c r="B517" s="9"/>
       <c r="C517" s="9"/>
@@ -7208,7 +7240,7 @@
       <c r="I517" s="3"/>
       <c r="J517" s="3"/>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518" s="14"/>
       <c r="B518" s="9"/>
       <c r="C518" s="9"/>
@@ -7220,7 +7252,7 @@
       <c r="I518" s="3"/>
       <c r="J518" s="3"/>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519" s="14"/>
       <c r="B519" s="9"/>
       <c r="C519" s="9"/>
@@ -7232,7 +7264,7 @@
       <c r="I519" s="3"/>
       <c r="J519" s="3"/>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A520" s="14"/>
       <c r="B520" s="9"/>
       <c r="C520" s="9"/>
@@ -7244,7 +7276,7 @@
       <c r="I520" s="3"/>
       <c r="J520" s="3"/>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A521" s="14"/>
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
@@ -7256,7 +7288,7 @@
       <c r="I521" s="3"/>
       <c r="J521" s="3"/>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A522" s="14"/>
       <c r="B522" s="9"/>
       <c r="C522" s="9"/>
@@ -7268,7 +7300,7 @@
       <c r="I522" s="3"/>
       <c r="J522" s="3"/>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A523" s="14"/>
       <c r="B523" s="9"/>
       <c r="C523" s="9"/>
@@ -7280,7 +7312,7 @@
       <c r="I523" s="3"/>
       <c r="J523" s="3"/>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524" s="14"/>
       <c r="B524" s="9"/>
       <c r="C524" s="9"/>
@@ -7292,7 +7324,7 @@
       <c r="I524" s="3"/>
       <c r="J524" s="3"/>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525" s="14"/>
       <c r="B525" s="9"/>
       <c r="C525" s="9"/>
@@ -7304,7 +7336,7 @@
       <c r="I525" s="3"/>
       <c r="J525" s="3"/>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526" s="14"/>
       <c r="B526" s="9"/>
       <c r="C526" s="9"/>
@@ -7316,7 +7348,7 @@
       <c r="I526" s="3"/>
       <c r="J526" s="3"/>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527" s="14"/>
       <c r="B527" s="9"/>
       <c r="C527" s="9"/>
@@ -7328,7 +7360,7 @@
       <c r="I527" s="3"/>
       <c r="J527" s="3"/>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A528" s="14"/>
       <c r="B528" s="9"/>
       <c r="C528" s="9"/>
@@ -7340,7 +7372,7 @@
       <c r="I528" s="3"/>
       <c r="J528" s="3"/>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A529" s="14"/>
       <c r="B529" s="9"/>
       <c r="C529" s="9"/>
@@ -7352,7 +7384,7 @@
       <c r="I529" s="3"/>
       <c r="J529" s="3"/>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A530" s="14"/>
       <c r="B530" s="9"/>
       <c r="C530" s="9"/>
@@ -7364,7 +7396,7 @@
       <c r="I530" s="3"/>
       <c r="J530" s="3"/>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A531" s="14"/>
       <c r="B531" s="9"/>
       <c r="C531" s="9"/>
@@ -7376,7 +7408,7 @@
       <c r="I531" s="3"/>
       <c r="J531" s="3"/>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A532" s="14"/>
       <c r="B532" s="9"/>
       <c r="C532" s="9"/>
@@ -7388,7 +7420,7 @@
       <c r="I532" s="3"/>
       <c r="J532" s="3"/>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A533" s="14"/>
       <c r="B533" s="9"/>
       <c r="C533" s="9"/>
@@ -7400,7 +7432,7 @@
       <c r="I533" s="3"/>
       <c r="J533" s="3"/>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A534" s="14"/>
       <c r="B534" s="9"/>
       <c r="C534" s="9"/>
@@ -7412,7 +7444,7 @@
       <c r="I534" s="3"/>
       <c r="J534" s="3"/>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A535" s="14"/>
       <c r="B535" s="9"/>
       <c r="C535" s="9"/>
@@ -7424,7 +7456,7 @@
       <c r="I535" s="3"/>
       <c r="J535" s="3"/>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A536" s="14"/>
       <c r="B536" s="9"/>
       <c r="C536" s="9"/>
@@ -7436,7 +7468,7 @@
       <c r="I536" s="3"/>
       <c r="J536" s="3"/>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A537" s="14"/>
       <c r="B537" s="9"/>
       <c r="C537" s="9"/>
@@ -7448,7 +7480,7 @@
       <c r="I537" s="3"/>
       <c r="J537" s="3"/>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A538" s="14"/>
       <c r="B538" s="9"/>
       <c r="C538" s="9"/>
@@ -7460,7 +7492,7 @@
       <c r="I538" s="3"/>
       <c r="J538" s="3"/>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A539" s="14"/>
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
@@ -7472,7 +7504,7 @@
       <c r="I539" s="3"/>
       <c r="J539" s="3"/>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A540" s="14"/>
       <c r="B540" s="9"/>
       <c r="C540" s="9"/>
@@ -7484,7 +7516,7 @@
       <c r="I540" s="3"/>
       <c r="J540" s="3"/>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A541" s="14"/>
       <c r="B541" s="9"/>
       <c r="C541" s="9"/>
@@ -7496,7 +7528,7 @@
       <c r="I541" s="3"/>
       <c r="J541" s="3"/>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A542" s="14"/>
       <c r="B542" s="9"/>
       <c r="C542" s="9"/>
@@ -7508,7 +7540,7 @@
       <c r="I542" s="3"/>
       <c r="J542" s="3"/>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A543" s="14"/>
       <c r="B543" s="9"/>
       <c r="C543" s="9"/>
@@ -7520,7 +7552,7 @@
       <c r="I543" s="3"/>
       <c r="J543" s="3"/>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A544" s="14"/>
       <c r="B544" s="9"/>
       <c r="C544" s="9"/>
@@ -7532,7 +7564,7 @@
       <c r="I544" s="3"/>
       <c r="J544" s="3"/>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A545" s="14"/>
       <c r="B545" s="9"/>
       <c r="C545" s="9"/>
@@ -7544,7 +7576,7 @@
       <c r="I545" s="3"/>
       <c r="J545" s="3"/>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A546" s="14"/>
       <c r="B546" s="9"/>
       <c r="C546" s="9"/>
@@ -7556,7 +7588,7 @@
       <c r="I546" s="3"/>
       <c r="J546" s="3"/>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A547" s="14"/>
       <c r="B547" s="9"/>
       <c r="C547" s="9"/>
@@ -7568,7 +7600,7 @@
       <c r="I547" s="3"/>
       <c r="J547" s="3"/>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A548" s="14"/>
       <c r="B548" s="9"/>
       <c r="C548" s="9"/>
@@ -7580,7 +7612,7 @@
       <c r="I548" s="3"/>
       <c r="J548" s="3"/>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A549" s="14"/>
       <c r="B549" s="9"/>
       <c r="C549" s="9"/>
@@ -7592,7 +7624,7 @@
       <c r="I549" s="3"/>
       <c r="J549" s="3"/>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A550" s="14"/>
       <c r="B550" s="9"/>
       <c r="C550" s="9"/>
@@ -7604,7 +7636,7 @@
       <c r="I550" s="3"/>
       <c r="J550" s="3"/>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A551" s="14"/>
       <c r="B551" s="9"/>
       <c r="C551" s="9"/>
@@ -7616,7 +7648,7 @@
       <c r="I551" s="3"/>
       <c r="J551" s="3"/>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A552" s="14"/>
       <c r="B552" s="9"/>
       <c r="C552" s="9"/>
@@ -7628,7 +7660,7 @@
       <c r="I552" s="3"/>
       <c r="J552" s="3"/>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A553" s="14"/>
       <c r="B553" s="9"/>
       <c r="C553" s="9"/>
@@ -7640,7 +7672,7 @@
       <c r="I553" s="3"/>
       <c r="J553" s="3"/>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A554" s="14"/>
       <c r="B554" s="9"/>
       <c r="C554" s="9"/>
@@ -7652,7 +7684,7 @@
       <c r="I554" s="3"/>
       <c r="J554" s="3"/>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A555" s="14"/>
       <c r="B555" s="9"/>
       <c r="C555" s="9"/>
@@ -7664,7 +7696,7 @@
       <c r="I555" s="3"/>
       <c r="J555" s="3"/>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A556" s="14"/>
       <c r="B556" s="9"/>
       <c r="C556" s="9"/>
@@ -7676,7 +7708,7 @@
       <c r="I556" s="3"/>
       <c r="J556" s="3"/>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A557" s="14"/>
       <c r="B557" s="9"/>
       <c r="C557" s="9"/>
@@ -7688,7 +7720,7 @@
       <c r="I557" s="3"/>
       <c r="J557" s="3"/>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A558" s="14"/>
       <c r="B558" s="9"/>
       <c r="C558" s="9"/>
@@ -7700,7 +7732,7 @@
       <c r="I558" s="3"/>
       <c r="J558" s="3"/>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A559" s="14"/>
       <c r="B559" s="9"/>
       <c r="C559" s="9"/>
@@ -7712,7 +7744,7 @@
       <c r="I559" s="3"/>
       <c r="J559" s="3"/>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A560" s="14"/>
       <c r="B560" s="9"/>
       <c r="C560" s="9"/>
@@ -7724,7 +7756,7 @@
       <c r="I560" s="3"/>
       <c r="J560" s="3"/>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A561" s="14"/>
       <c r="B561" s="9"/>
       <c r="C561" s="9"/>
@@ -7736,7 +7768,7 @@
       <c r="I561" s="3"/>
       <c r="J561" s="3"/>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A562" s="14"/>
       <c r="B562" s="9"/>
       <c r="C562" s="9"/>
@@ -7748,7 +7780,7 @@
       <c r="I562" s="3"/>
       <c r="J562" s="3"/>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A563" s="14"/>
       <c r="B563" s="9"/>
       <c r="C563" s="9"/>
@@ -7760,7 +7792,7 @@
       <c r="I563" s="3"/>
       <c r="J563" s="3"/>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A564" s="14"/>
       <c r="B564" s="9"/>
       <c r="C564" s="9"/>
@@ -7772,7 +7804,7 @@
       <c r="I564" s="3"/>
       <c r="J564" s="3"/>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A565" s="14"/>
       <c r="B565" s="9"/>
       <c r="C565" s="9"/>
@@ -7784,7 +7816,7 @@
       <c r="I565" s="3"/>
       <c r="J565" s="3"/>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A566" s="14"/>
       <c r="B566" s="9"/>
       <c r="C566" s="9"/>
@@ -7796,7 +7828,7 @@
       <c r="I566" s="3"/>
       <c r="J566" s="3"/>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A567" s="14"/>
       <c r="B567" s="9"/>
       <c r="C567" s="9"/>
@@ -7808,7 +7840,7 @@
       <c r="I567" s="3"/>
       <c r="J567" s="3"/>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A568" s="14"/>
       <c r="B568" s="9"/>
       <c r="C568" s="9"/>
@@ -7820,7 +7852,7 @@
       <c r="I568" s="3"/>
       <c r="J568" s="3"/>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A569" s="14"/>
       <c r="B569" s="9"/>
       <c r="C569" s="9"/>
@@ -7832,7 +7864,7 @@
       <c r="I569" s="3"/>
       <c r="J569" s="3"/>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A570" s="14"/>
       <c r="B570" s="9"/>
       <c r="C570" s="9"/>
@@ -7844,7 +7876,7 @@
       <c r="I570" s="3"/>
       <c r="J570" s="3"/>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A571" s="14"/>
       <c r="B571" s="9"/>
       <c r="C571" s="9"/>
@@ -7856,7 +7888,7 @@
       <c r="I571" s="3"/>
       <c r="J571" s="3"/>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A572" s="14"/>
       <c r="B572" s="9"/>
       <c r="C572" s="9"/>
@@ -7868,7 +7900,7 @@
       <c r="I572" s="3"/>
       <c r="J572" s="3"/>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A573" s="14"/>
       <c r="B573" s="9"/>
       <c r="C573" s="9"/>
@@ -7880,7 +7912,7 @@
       <c r="I573" s="3"/>
       <c r="J573" s="3"/>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A574" s="14"/>
       <c r="B574" s="9"/>
       <c r="C574" s="9"/>
@@ -7892,7 +7924,7 @@
       <c r="I574" s="3"/>
       <c r="J574" s="3"/>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A575" s="14"/>
       <c r="B575" s="9"/>
       <c r="C575" s="9"/>
@@ -7904,7 +7936,7 @@
       <c r="I575" s="3"/>
       <c r="J575" s="3"/>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A576" s="14"/>
       <c r="B576" s="9"/>
       <c r="C576" s="9"/>
@@ -7916,7 +7948,7 @@
       <c r="I576" s="3"/>
       <c r="J576" s="3"/>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A577" s="14"/>
       <c r="B577" s="9"/>
       <c r="C577" s="9"/>
@@ -7928,7 +7960,7 @@
       <c r="I577" s="3"/>
       <c r="J577" s="3"/>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A578" s="14"/>
       <c r="B578" s="9"/>
       <c r="C578" s="9"/>
@@ -7940,7 +7972,7 @@
       <c r="I578" s="3"/>
       <c r="J578" s="3"/>
     </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A579" s="14"/>
       <c r="B579" s="9"/>
       <c r="C579" s="9"/>
@@ -7952,7 +7984,7 @@
       <c r="I579" s="3"/>
       <c r="J579" s="3"/>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A580" s="14"/>
       <c r="B580" s="9"/>
       <c r="C580" s="9"/>
@@ -7964,7 +7996,7 @@
       <c r="I580" s="3"/>
       <c r="J580" s="3"/>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A581" s="14"/>
       <c r="B581" s="9"/>
       <c r="C581" s="9"/>
@@ -7976,7 +8008,7 @@
       <c r="I581" s="3"/>
       <c r="J581" s="3"/>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A582" s="14"/>
       <c r="B582" s="9"/>
       <c r="C582" s="9"/>
@@ -7988,7 +8020,7 @@
       <c r="I582" s="3"/>
       <c r="J582" s="3"/>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A583" s="14"/>
       <c r="B583" s="9"/>
       <c r="C583" s="9"/>
@@ -8000,7 +8032,7 @@
       <c r="I583" s="3"/>
       <c r="J583" s="3"/>
     </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A584" s="14"/>
       <c r="B584" s="9"/>
       <c r="C584" s="9"/>
@@ -8012,7 +8044,7 @@
       <c r="I584" s="3"/>
       <c r="J584" s="3"/>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A585" s="14"/>
       <c r="B585" s="9"/>
       <c r="C585" s="9"/>
@@ -8024,7 +8056,7 @@
       <c r="I585" s="3"/>
       <c r="J585" s="3"/>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A586" s="14"/>
       <c r="B586" s="9"/>
       <c r="C586" s="9"/>
@@ -8036,7 +8068,7 @@
       <c r="I586" s="3"/>
       <c r="J586" s="3"/>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A587" s="14"/>
       <c r="B587" s="9"/>
       <c r="C587" s="9"/>
@@ -8048,7 +8080,7 @@
       <c r="I587" s="3"/>
       <c r="J587" s="3"/>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A588" s="14"/>
       <c r="B588" s="9"/>
       <c r="C588" s="9"/>
@@ -8060,7 +8092,7 @@
       <c r="I588" s="3"/>
       <c r="J588" s="3"/>
     </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A589" s="14"/>
       <c r="B589" s="9"/>
       <c r="C589" s="9"/>
@@ -8072,7 +8104,7 @@
       <c r="I589" s="3"/>
       <c r="J589" s="3"/>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A590" s="14"/>
       <c r="B590" s="9"/>
       <c r="C590" s="9"/>
@@ -8084,7 +8116,7 @@
       <c r="I590" s="3"/>
       <c r="J590" s="3"/>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A591" s="14"/>
       <c r="B591" s="9"/>
       <c r="C591" s="9"/>
@@ -8096,7 +8128,7 @@
       <c r="I591" s="3"/>
       <c r="J591" s="3"/>
     </row>
-    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A592" s="14"/>
       <c r="B592" s="9"/>
       <c r="C592" s="9"/>
@@ -8108,7 +8140,7 @@
       <c r="I592" s="3"/>
       <c r="J592" s="3"/>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A593" s="14"/>
       <c r="B593" s="9"/>
       <c r="C593" s="9"/>
@@ -8120,7 +8152,7 @@
       <c r="I593" s="3"/>
       <c r="J593" s="3"/>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A594" s="14"/>
       <c r="B594" s="9"/>
       <c r="C594" s="9"/>
@@ -8132,7 +8164,7 @@
       <c r="I594" s="3"/>
       <c r="J594" s="3"/>
     </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A595" s="14"/>
       <c r="B595" s="9"/>
       <c r="C595" s="9"/>
@@ -8144,7 +8176,7 @@
       <c r="I595" s="3"/>
       <c r="J595" s="3"/>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A596" s="14"/>
       <c r="B596" s="9"/>
       <c r="C596" s="9"/>
@@ -8156,7 +8188,7 @@
       <c r="I596" s="3"/>
       <c r="J596" s="3"/>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A597" s="14"/>
       <c r="B597" s="9"/>
       <c r="C597" s="9"/>
@@ -8168,7 +8200,7 @@
       <c r="I597" s="3"/>
       <c r="J597" s="3"/>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A598" s="14"/>
       <c r="B598" s="9"/>
       <c r="C598" s="9"/>
@@ -8180,7 +8212,7 @@
       <c r="I598" s="3"/>
       <c r="J598" s="3"/>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A599" s="14"/>
       <c r="B599" s="9"/>
       <c r="C599" s="9"/>
@@ -8192,7 +8224,7 @@
       <c r="I599" s="3"/>
       <c r="J599" s="3"/>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A600" s="14"/>
       <c r="B600" s="9"/>
       <c r="C600" s="9"/>
@@ -8204,7 +8236,7 @@
       <c r="I600" s="3"/>
       <c r="J600" s="3"/>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A601" s="14"/>
       <c r="B601" s="9"/>
       <c r="C601" s="9"/>
@@ -8216,7 +8248,7 @@
       <c r="I601" s="3"/>
       <c r="J601" s="3"/>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A602" s="14"/>
       <c r="B602" s="9"/>
       <c r="C602" s="9"/>
@@ -8228,7 +8260,7 @@
       <c r="I602" s="3"/>
       <c r="J602" s="3"/>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A603" s="14"/>
       <c r="B603" s="9"/>
       <c r="C603" s="9"/>
@@ -8240,7 +8272,7 @@
       <c r="I603" s="3"/>
       <c r="J603" s="3"/>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A604" s="14"/>
       <c r="B604" s="9"/>
       <c r="C604" s="9"/>
@@ -8252,7 +8284,7 @@
       <c r="I604" s="3"/>
       <c r="J604" s="3"/>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A605" s="14"/>
       <c r="B605" s="9"/>
       <c r="C605" s="9"/>
@@ -8264,7 +8296,7 @@
       <c r="I605" s="3"/>
       <c r="J605" s="3"/>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A606" s="14"/>
       <c r="B606" s="9"/>
       <c r="C606" s="9"/>
@@ -8276,7 +8308,7 @@
       <c r="I606" s="3"/>
       <c r="J606" s="3"/>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A607" s="14"/>
       <c r="B607" s="9"/>
       <c r="C607" s="9"/>
@@ -8288,7 +8320,7 @@
       <c r="I607" s="3"/>
       <c r="J607" s="3"/>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A608" s="14"/>
       <c r="B608" s="9"/>
       <c r="C608" s="9"/>
@@ -8300,7 +8332,7 @@
       <c r="I608" s="3"/>
       <c r="J608" s="3"/>
     </row>
-    <row r="609" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A609" s="14"/>
       <c r="B609" s="9"/>
       <c r="C609" s="9"/>
@@ -8312,7 +8344,7 @@
       <c r="I609" s="3"/>
       <c r="J609" s="3"/>
     </row>
-    <row r="610" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A610" s="14"/>
       <c r="B610" s="9"/>
       <c r="C610" s="9"/>
@@ -8324,7 +8356,7 @@
       <c r="I610" s="3"/>
       <c r="J610" s="3"/>
     </row>
-    <row r="611" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A611" s="14"/>
       <c r="B611" s="9"/>
       <c r="C611" s="9"/>
@@ -8336,7 +8368,7 @@
       <c r="I611" s="3"/>
       <c r="J611" s="3"/>
     </row>
-    <row r="612" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A612" s="14"/>
       <c r="B612" s="9"/>
       <c r="C612" s="9"/>
@@ -8348,7 +8380,7 @@
       <c r="I612" s="3"/>
       <c r="J612" s="3"/>
     </row>
-    <row r="613" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A613" s="14"/>
       <c r="B613" s="9"/>
       <c r="C613" s="9"/>
@@ -8360,7 +8392,7 @@
       <c r="I613" s="3"/>
       <c r="J613" s="3"/>
     </row>
-    <row r="614" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A614" s="14"/>
       <c r="B614" s="9"/>
       <c r="C614" s="9"/>
@@ -8372,7 +8404,7 @@
       <c r="I614" s="3"/>
       <c r="J614" s="3"/>
     </row>
-    <row r="615" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A615" s="14"/>
       <c r="B615" s="9"/>
       <c r="C615" s="9"/>
@@ -8384,7 +8416,7 @@
       <c r="I615" s="3"/>
       <c r="J615" s="3"/>
     </row>
-    <row r="616" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A616" s="14"/>
       <c r="B616" s="9"/>
       <c r="C616" s="9"/>
@@ -8396,7 +8428,7 @@
       <c r="I616" s="3"/>
       <c r="J616" s="3"/>
     </row>
-    <row r="617" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A617" s="14"/>
       <c r="B617" s="9"/>
       <c r="C617" s="9"/>
@@ -8408,7 +8440,7 @@
       <c r="I617" s="3"/>
       <c r="J617" s="3"/>
     </row>
-    <row r="618" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A618" s="14"/>
       <c r="B618" s="9"/>
       <c r="C618" s="9"/>
@@ -8420,7 +8452,7 @@
       <c r="I618" s="3"/>
       <c r="J618" s="3"/>
     </row>
-    <row r="619" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A619" s="14"/>
       <c r="B619" s="9"/>
       <c r="C619" s="9"/>
@@ -8432,7 +8464,7 @@
       <c r="I619" s="3"/>
       <c r="J619" s="3"/>
     </row>
-    <row r="620" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A620" s="14"/>
       <c r="B620" s="9"/>
       <c r="C620" s="9"/>
@@ -8444,7 +8476,7 @@
       <c r="I620" s="3"/>
       <c r="J620" s="3"/>
     </row>
-    <row r="621" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A621" s="14"/>
       <c r="B621" s="9"/>
       <c r="C621" s="9"/>
@@ -8456,7 +8488,7 @@
       <c r="I621" s="3"/>
       <c r="J621" s="3"/>
     </row>
-    <row r="622" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A622" s="14"/>
       <c r="B622" s="9"/>
       <c r="C622" s="9"/>
@@ -8468,7 +8500,7 @@
       <c r="I622" s="3"/>
       <c r="J622" s="3"/>
     </row>
-    <row r="623" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A623" s="14"/>
       <c r="B623" s="9"/>
       <c r="C623" s="9"/>
@@ -8480,7 +8512,7 @@
       <c r="I623" s="3"/>
       <c r="J623" s="3"/>
     </row>
-    <row r="624" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A624" s="14"/>
       <c r="B624" s="9"/>
       <c r="C624" s="9"/>
@@ -8492,7 +8524,7 @@
       <c r="I624" s="3"/>
       <c r="J624" s="3"/>
     </row>
-    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A625" s="14"/>
       <c r="B625" s="9"/>
       <c r="C625" s="9"/>
@@ -8504,7 +8536,7 @@
       <c r="I625" s="3"/>
       <c r="J625" s="3"/>
     </row>
-    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A626" s="14"/>
       <c r="B626" s="9"/>
       <c r="C626" s="9"/>
@@ -8516,7 +8548,7 @@
       <c r="I626" s="3"/>
       <c r="J626" s="3"/>
     </row>
-    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A627" s="14"/>
       <c r="B627" s="9"/>
       <c r="C627" s="9"/>
@@ -8528,7 +8560,7 @@
       <c r="I627" s="3"/>
       <c r="J627" s="3"/>
     </row>
-    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A628" s="14"/>
       <c r="B628" s="9"/>
       <c r="C628" s="9"/>
@@ -8540,7 +8572,7 @@
       <c r="I628" s="3"/>
       <c r="J628" s="3"/>
     </row>
-    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A629" s="14"/>
       <c r="B629" s="9"/>
       <c r="C629" s="9"/>
@@ -8552,7 +8584,7 @@
       <c r="I629" s="3"/>
       <c r="J629" s="3"/>
     </row>
-    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A630" s="14"/>
       <c r="B630" s="9"/>
       <c r="C630" s="9"/>
@@ -8564,7 +8596,7 @@
       <c r="I630" s="3"/>
       <c r="J630" s="3"/>
     </row>
-    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A631" s="14"/>
       <c r="B631" s="9"/>
       <c r="C631" s="9"/>
@@ -8576,7 +8608,7 @@
       <c r="I631" s="3"/>
       <c r="J631" s="3"/>
     </row>
-    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A632" s="14"/>
       <c r="B632" s="9"/>
       <c r="C632" s="9"/>
@@ -8588,7 +8620,7 @@
       <c r="I632" s="3"/>
       <c r="J632" s="3"/>
     </row>
-    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A633" s="14"/>
       <c r="B633" s="9"/>
       <c r="C633" s="9"/>
@@ -8600,7 +8632,7 @@
       <c r="I633" s="3"/>
       <c r="J633" s="3"/>
     </row>
-    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A634" s="14"/>
       <c r="B634" s="9"/>
       <c r="C634" s="9"/>
@@ -8612,7 +8644,7 @@
       <c r="I634" s="3"/>
       <c r="J634" s="3"/>
     </row>
-    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A635" s="14"/>
       <c r="B635" s="9"/>
       <c r="C635" s="9"/>
@@ -8624,7 +8656,7 @@
       <c r="I635" s="3"/>
       <c r="J635" s="3"/>
     </row>
-    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A636" s="14"/>
       <c r="B636" s="9"/>
       <c r="C636" s="9"/>
@@ -8636,7 +8668,7 @@
       <c r="I636" s="3"/>
       <c r="J636" s="3"/>
     </row>
-    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A637" s="14"/>
       <c r="B637" s="9"/>
       <c r="C637" s="9"/>
@@ -8648,7 +8680,7 @@
       <c r="I637" s="3"/>
       <c r="J637" s="3"/>
     </row>
-    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A638" s="14"/>
       <c r="B638" s="9"/>
       <c r="C638" s="9"/>
@@ -8660,7 +8692,7 @@
       <c r="I638" s="3"/>
       <c r="J638" s="3"/>
     </row>
-    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A639" s="14"/>
       <c r="B639" s="9"/>
       <c r="C639" s="9"/>
@@ -8672,7 +8704,7 @@
       <c r="I639" s="3"/>
       <c r="J639" s="3"/>
     </row>
-    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A640" s="14"/>
       <c r="B640" s="9"/>
       <c r="C640" s="9"/>
@@ -8684,7 +8716,7 @@
       <c r="I640" s="3"/>
       <c r="J640" s="3"/>
     </row>
-    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A641" s="14"/>
       <c r="B641" s="9"/>
       <c r="C641" s="9"/>
@@ -8696,7 +8728,7 @@
       <c r="I641" s="3"/>
       <c r="J641" s="3"/>
     </row>
-    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A642" s="14"/>
       <c r="B642" s="9"/>
       <c r="C642" s="9"/>
@@ -8708,7 +8740,7 @@
       <c r="I642" s="3"/>
       <c r="J642" s="3"/>
     </row>
-    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A643" s="14"/>
       <c r="B643" s="9"/>
       <c r="C643" s="9"/>
@@ -8720,7 +8752,7 @@
       <c r="I643" s="3"/>
       <c r="J643" s="3"/>
     </row>
-    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A644" s="14"/>
       <c r="B644" s="9"/>
       <c r="C644" s="9"/>
@@ -8732,7 +8764,7 @@
       <c r="I644" s="3"/>
       <c r="J644" s="3"/>
     </row>
-    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A645" s="14"/>
       <c r="B645" s="9"/>
       <c r="C645" s="9"/>
@@ -8744,7 +8776,7 @@
       <c r="I645" s="3"/>
       <c r="J645" s="3"/>
     </row>
-    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A646" s="14"/>
       <c r="B646" s="9"/>
       <c r="C646" s="9"/>
@@ -8756,7 +8788,7 @@
       <c r="I646" s="3"/>
       <c r="J646" s="3"/>
     </row>
-    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A647" s="14"/>
       <c r="B647" s="9"/>
       <c r="C647" s="9"/>
@@ -8768,7 +8800,7 @@
       <c r="I647" s="3"/>
       <c r="J647" s="3"/>
     </row>
-    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A648" s="14"/>
       <c r="B648" s="9"/>
       <c r="C648" s="9"/>
@@ -8780,7 +8812,7 @@
       <c r="I648" s="3"/>
       <c r="J648" s="3"/>
     </row>
-    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A649" s="14"/>
       <c r="B649" s="9"/>
       <c r="C649" s="9"/>
@@ -8792,7 +8824,7 @@
       <c r="I649" s="3"/>
       <c r="J649" s="3"/>
     </row>
-    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A650" s="14"/>
       <c r="B650" s="9"/>
       <c r="C650" s="9"/>
@@ -8804,7 +8836,7 @@
       <c r="I650" s="3"/>
       <c r="J650" s="3"/>
     </row>
-    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A651" s="14"/>
       <c r="B651" s="9"/>
       <c r="C651" s="9"/>
@@ -8816,7 +8848,7 @@
       <c r="I651" s="3"/>
       <c r="J651" s="3"/>
     </row>
-    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A652" s="14"/>
       <c r="B652" s="9"/>
       <c r="C652" s="9"/>
@@ -8828,7 +8860,7 @@
       <c r="I652" s="3"/>
       <c r="J652" s="3"/>
     </row>
-    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A653" s="14"/>
       <c r="B653" s="9"/>
       <c r="C653" s="9"/>
@@ -8840,7 +8872,7 @@
       <c r="I653" s="3"/>
       <c r="J653" s="3"/>
     </row>
-    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A654" s="14"/>
       <c r="B654" s="9"/>
       <c r="C654" s="9"/>
@@ -8852,7 +8884,7 @@
       <c r="I654" s="3"/>
       <c r="J654" s="3"/>
     </row>
-    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A655" s="14"/>
       <c r="B655" s="9"/>
       <c r="C655" s="9"/>
@@ -8864,7 +8896,7 @@
       <c r="I655" s="3"/>
       <c r="J655" s="3"/>
     </row>
-    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A656" s="14"/>
       <c r="B656" s="9"/>
       <c r="C656" s="9"/>
@@ -8876,7 +8908,7 @@
       <c r="I656" s="3"/>
       <c r="J656" s="3"/>
     </row>
-    <row r="657" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A657" s="14"/>
       <c r="B657" s="9"/>
       <c r="C657" s="9"/>
@@ -8888,7 +8920,7 @@
       <c r="I657" s="3"/>
       <c r="J657" s="3"/>
     </row>
-    <row r="658" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A658" s="14"/>
       <c r="B658" s="9"/>
       <c r="C658" s="9"/>
@@ -8900,7 +8932,7 @@
       <c r="I658" s="3"/>
       <c r="J658" s="3"/>
     </row>
-    <row r="659" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A659" s="14"/>
       <c r="B659" s="9"/>
       <c r="C659" s="9"/>
@@ -8912,7 +8944,7 @@
       <c r="I659" s="3"/>
       <c r="J659" s="3"/>
     </row>
-    <row r="660" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A660" s="14"/>
       <c r="B660" s="9"/>
       <c r="C660" s="9"/>
@@ -8924,7 +8956,7 @@
       <c r="I660" s="3"/>
       <c r="J660" s="3"/>
     </row>
-    <row r="661" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A661" s="14"/>
       <c r="B661" s="9"/>
       <c r="C661" s="9"/>
@@ -8936,7 +8968,7 @@
       <c r="I661" s="3"/>
       <c r="J661" s="3"/>
     </row>
-    <row r="662" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A662" s="14"/>
       <c r="B662" s="9"/>
       <c r="C662" s="9"/>
@@ -8948,7 +8980,7 @@
       <c r="I662" s="3"/>
       <c r="J662" s="3"/>
     </row>
-    <row r="663" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A663" s="14"/>
       <c r="B663" s="9"/>
       <c r="C663" s="9"/>
@@ -8960,7 +8992,7 @@
       <c r="I663" s="3"/>
       <c r="J663" s="3"/>
     </row>
-    <row r="664" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A664" s="14"/>
       <c r="B664" s="9"/>
       <c r="C664" s="9"/>
@@ -8972,7 +9004,7 @@
       <c r="I664" s="3"/>
       <c r="J664" s="3"/>
     </row>
-    <row r="665" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A665" s="14"/>
       <c r="B665" s="9"/>
       <c r="C665" s="9"/>
@@ -8984,7 +9016,7 @@
       <c r="I665" s="3"/>
       <c r="J665" s="3"/>
     </row>
-    <row r="666" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A666" s="14"/>
       <c r="B666" s="9"/>
       <c r="C666" s="9"/>
@@ -8996,7 +9028,7 @@
       <c r="I666" s="3"/>
       <c r="J666" s="3"/>
     </row>
-    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A667" s="14"/>
       <c r="B667" s="9"/>
       <c r="C667" s="9"/>
@@ -9008,7 +9040,7 @@
       <c r="I667" s="3"/>
       <c r="J667" s="3"/>
     </row>
-    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A668" s="14"/>
       <c r="B668" s="9"/>
       <c r="C668" s="9"/>
@@ -9020,7 +9052,7 @@
       <c r="I668" s="3"/>
       <c r="J668" s="3"/>
     </row>
-    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A669" s="14"/>
       <c r="B669" s="9"/>
       <c r="C669" s="9"/>
@@ -9032,7 +9064,7 @@
       <c r="I669" s="3"/>
       <c r="J669" s="3"/>
     </row>
-    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A670" s="14"/>
       <c r="B670" s="9"/>
       <c r="C670" s="9"/>
@@ -9044,7 +9076,7 @@
       <c r="I670" s="3"/>
       <c r="J670" s="3"/>
     </row>
-    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A671" s="14"/>
       <c r="B671" s="9"/>
       <c r="C671" s="9"/>
@@ -9056,7 +9088,7 @@
       <c r="I671" s="3"/>
       <c r="J671" s="3"/>
     </row>
-    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A672" s="14"/>
       <c r="B672" s="9"/>
       <c r="C672" s="9"/>
@@ -9068,7 +9100,7 @@
       <c r="I672" s="3"/>
       <c r="J672" s="3"/>
     </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A673" s="14"/>
       <c r="B673" s="9"/>
       <c r="C673" s="9"/>
@@ -9080,7 +9112,7 @@
       <c r="I673" s="3"/>
       <c r="J673" s="3"/>
     </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A674" s="14"/>
       <c r="B674" s="9"/>
       <c r="C674" s="9"/>
@@ -9092,7 +9124,7 @@
       <c r="I674" s="3"/>
       <c r="J674" s="3"/>
     </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A675" s="14"/>
       <c r="B675" s="9"/>
       <c r="C675" s="9"/>
@@ -9104,7 +9136,7 @@
       <c r="I675" s="3"/>
       <c r="J675" s="3"/>
     </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A676" s="14"/>
       <c r="B676" s="9"/>
       <c r="C676" s="9"/>
@@ -9116,7 +9148,7 @@
       <c r="I676" s="3"/>
       <c r="J676" s="3"/>
     </row>
-    <row r="677" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A677" s="14"/>
       <c r="B677" s="9"/>
       <c r="C677" s="9"/>
@@ -9128,7 +9160,7 @@
       <c r="I677" s="3"/>
       <c r="J677" s="3"/>
     </row>
-    <row r="678" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A678" s="14"/>
       <c r="B678" s="9"/>
       <c r="C678" s="9"/>
@@ -9140,7 +9172,7 @@
       <c r="I678" s="3"/>
       <c r="J678" s="3"/>
     </row>
-    <row r="679" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A679" s="14"/>
       <c r="B679" s="9"/>
       <c r="C679" s="9"/>
@@ -9152,7 +9184,7 @@
       <c r="I679" s="3"/>
       <c r="J679" s="3"/>
     </row>
-    <row r="680" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A680" s="14"/>
       <c r="B680" s="9"/>
       <c r="C680" s="9"/>
@@ -9164,7 +9196,7 @@
       <c r="I680" s="3"/>
       <c r="J680" s="3"/>
     </row>
-    <row r="681" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A681" s="14"/>
       <c r="B681" s="9"/>
       <c r="C681" s="9"/>
@@ -9176,7 +9208,7 @@
       <c r="I681" s="3"/>
       <c r="J681" s="3"/>
     </row>
-    <row r="682" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A682" s="14"/>
       <c r="B682" s="9"/>
       <c r="C682" s="9"/>
@@ -9188,7 +9220,7 @@
       <c r="I682" s="3"/>
       <c r="J682" s="3"/>
     </row>
-    <row r="683" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A683" s="14"/>
       <c r="B683" s="9"/>
       <c r="C683" s="9"/>
@@ -9200,7 +9232,7 @@
       <c r="I683" s="3"/>
       <c r="J683" s="3"/>
     </row>
-    <row r="684" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A684" s="14"/>
       <c r="B684" s="9"/>
       <c r="C684" s="9"/>
@@ -9212,7 +9244,7 @@
       <c r="I684" s="3"/>
       <c r="J684" s="3"/>
     </row>
-    <row r="685" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A685" s="14"/>
       <c r="B685" s="9"/>
       <c r="C685" s="9"/>
@@ -9224,7 +9256,7 @@
       <c r="I685" s="3"/>
       <c r="J685" s="3"/>
     </row>
-    <row r="686" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A686" s="14"/>
       <c r="B686" s="9"/>
       <c r="C686" s="9"/>
@@ -9236,7 +9268,7 @@
       <c r="I686" s="3"/>
       <c r="J686" s="3"/>
     </row>
-    <row r="687" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A687" s="14"/>
       <c r="B687" s="9"/>
       <c r="C687" s="9"/>
@@ -9248,7 +9280,7 @@
       <c r="I687" s="3"/>
       <c r="J687" s="3"/>
     </row>
-    <row r="688" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A688" s="14"/>
       <c r="B688" s="9"/>
       <c r="C688" s="9"/>
@@ -9260,7 +9292,7 @@
       <c r="I688" s="3"/>
       <c r="J688" s="3"/>
     </row>
-    <row r="689" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A689" s="14"/>
       <c r="B689" s="9"/>
       <c r="C689" s="9"/>
@@ -9272,7 +9304,7 @@
       <c r="I689" s="3"/>
       <c r="J689" s="3"/>
     </row>
-    <row r="690" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A690" s="14"/>
       <c r="B690" s="9"/>
       <c r="C690" s="9"/>
@@ -9284,7 +9316,7 @@
       <c r="I690" s="3"/>
       <c r="J690" s="3"/>
     </row>
-    <row r="691" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A691" s="14"/>
       <c r="B691" s="9"/>
       <c r="C691" s="9"/>
@@ -9296,7 +9328,7 @@
       <c r="I691" s="3"/>
       <c r="J691" s="3"/>
     </row>
-    <row r="692" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A692" s="14"/>
       <c r="B692" s="9"/>
       <c r="C692" s="9"/>
@@ -9308,7 +9340,7 @@
       <c r="I692" s="3"/>
       <c r="J692" s="3"/>
     </row>
-    <row r="693" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A693" s="14"/>
       <c r="B693" s="9"/>
       <c r="C693" s="9"/>
@@ -9320,7 +9352,7 @@
       <c r="I693" s="3"/>
       <c r="J693" s="3"/>
     </row>
-    <row r="694" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A694" s="14"/>
       <c r="B694" s="9"/>
       <c r="C694" s="9"/>
@@ -9332,7 +9364,7 @@
       <c r="I694" s="3"/>
       <c r="J694" s="3"/>
     </row>
-    <row r="695" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A695" s="14"/>
       <c r="B695" s="9"/>
       <c r="C695" s="9"/>
@@ -9344,7 +9376,7 @@
       <c r="I695" s="3"/>
       <c r="J695" s="3"/>
     </row>
-    <row r="696" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A696" s="14"/>
       <c r="B696" s="9"/>
       <c r="C696" s="9"/>
@@ -9356,7 +9388,7 @@
       <c r="I696" s="3"/>
       <c r="J696" s="3"/>
     </row>
-    <row r="697" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A697" s="14"/>
       <c r="B697" s="9"/>
       <c r="C697" s="9"/>
@@ -9368,7 +9400,7 @@
       <c r="I697" s="3"/>
       <c r="J697" s="3"/>
     </row>
-    <row r="698" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A698" s="14"/>
       <c r="B698" s="9"/>
       <c r="C698" s="9"/>
@@ -9380,7 +9412,7 @@
       <c r="I698" s="3"/>
       <c r="J698" s="3"/>
     </row>
-    <row r="699" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A699" s="14"/>
       <c r="B699" s="9"/>
       <c r="C699" s="9"/>
@@ -9392,7 +9424,7 @@
       <c r="I699" s="3"/>
       <c r="J699" s="3"/>
     </row>
-    <row r="700" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A700" s="14"/>
       <c r="B700" s="9"/>
       <c r="C700" s="9"/>
@@ -9404,7 +9436,7 @@
       <c r="I700" s="3"/>
       <c r="J700" s="3"/>
     </row>
-    <row r="701" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A701" s="14"/>
       <c r="B701" s="9"/>
       <c r="C701" s="9"/>
@@ -9416,7 +9448,7 @@
       <c r="I701" s="3"/>
       <c r="J701" s="3"/>
     </row>
-    <row r="702" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A702" s="14"/>
       <c r="B702" s="9"/>
       <c r="C702" s="9"/>
@@ -9428,7 +9460,7 @@
       <c r="I702" s="3"/>
       <c r="J702" s="3"/>
     </row>
-    <row r="703" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A703" s="14"/>
       <c r="B703" s="9"/>
       <c r="C703" s="9"/>
@@ -9440,7 +9472,7 @@
       <c r="I703" s="3"/>
       <c r="J703" s="3"/>
     </row>
-    <row r="704" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A704" s="14"/>
       <c r="B704" s="9"/>
       <c r="C704" s="9"/>
@@ -9452,7 +9484,7 @@
       <c r="I704" s="3"/>
       <c r="J704" s="3"/>
     </row>
-    <row r="705" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A705" s="14"/>
       <c r="B705" s="9"/>
       <c r="C705" s="9"/>
@@ -9464,7 +9496,7 @@
       <c r="I705" s="3"/>
       <c r="J705" s="3"/>
     </row>
-    <row r="706" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A706" s="14"/>
       <c r="B706" s="9"/>
       <c r="C706" s="9"/>
@@ -9476,7 +9508,7 @@
       <c r="I706" s="3"/>
       <c r="J706" s="3"/>
     </row>
-    <row r="707" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A707" s="14"/>
       <c r="B707" s="9"/>
       <c r="C707" s="9"/>
@@ -9488,7 +9520,7 @@
       <c r="I707" s="3"/>
       <c r="J707" s="3"/>
     </row>
-    <row r="708" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A708" s="14"/>
       <c r="B708" s="9"/>
       <c r="C708" s="9"/>
@@ -9500,7 +9532,7 @@
       <c r="I708" s="3"/>
       <c r="J708" s="3"/>
     </row>
-    <row r="709" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A709" s="14"/>
       <c r="B709" s="9"/>
       <c r="C709" s="9"/>
@@ -9512,7 +9544,7 @@
       <c r="I709" s="3"/>
       <c r="J709" s="3"/>
     </row>
-    <row r="710" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A710" s="14"/>
       <c r="B710" s="9"/>
       <c r="C710" s="9"/>
@@ -9524,7 +9556,7 @@
       <c r="I710" s="3"/>
       <c r="J710" s="3"/>
     </row>
-    <row r="711" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A711" s="14"/>
       <c r="B711" s="9"/>
       <c r="C711" s="9"/>
@@ -9536,7 +9568,7 @@
       <c r="I711" s="3"/>
       <c r="J711" s="3"/>
     </row>
-    <row r="712" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A712" s="14"/>
       <c r="B712" s="9"/>
       <c r="C712" s="9"/>
@@ -9548,7 +9580,7 @@
       <c r="I712" s="3"/>
       <c r="J712" s="3"/>
     </row>
-    <row r="713" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A713" s="14"/>
       <c r="B713" s="9"/>
       <c r="C713" s="9"/>
@@ -9560,7 +9592,7 @@
       <c r="I713" s="3"/>
       <c r="J713" s="3"/>
     </row>
-    <row r="714" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A714" s="14"/>
       <c r="B714" s="9"/>
       <c r="C714" s="9"/>
@@ -9572,7 +9604,7 @@
       <c r="I714" s="3"/>
       <c r="J714" s="3"/>
     </row>
-    <row r="715" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A715" s="14"/>
       <c r="B715" s="9"/>
       <c r="C715" s="9"/>
@@ -9584,7 +9616,7 @@
       <c r="I715" s="3"/>
       <c r="J715" s="3"/>
     </row>
-    <row r="716" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A716" s="14"/>
       <c r="B716" s="9"/>
       <c r="C716" s="9"/>
@@ -9596,7 +9628,7 @@
       <c r="I716" s="3"/>
       <c r="J716" s="3"/>
     </row>
-    <row r="717" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A717" s="14"/>
       <c r="B717" s="9"/>
       <c r="C717" s="9"/>
@@ -9608,7 +9640,7 @@
       <c r="I717" s="3"/>
       <c r="J717" s="3"/>
     </row>
-    <row r="718" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A718" s="14"/>
       <c r="B718" s="9"/>
       <c r="C718" s="9"/>
@@ -9620,7 +9652,7 @@
       <c r="I718" s="3"/>
       <c r="J718" s="3"/>
     </row>
-    <row r="719" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A719" s="14"/>
       <c r="B719" s="9"/>
       <c r="C719" s="9"/>
@@ -9632,7 +9664,7 @@
       <c r="I719" s="3"/>
       <c r="J719" s="3"/>
     </row>
-    <row r="720" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A720" s="14"/>
       <c r="B720" s="9"/>
       <c r="C720" s="9"/>
@@ -9644,7 +9676,7 @@
       <c r="I720" s="3"/>
       <c r="J720" s="3"/>
     </row>
-    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A721" s="14"/>
       <c r="B721" s="9"/>
       <c r="C721" s="9"/>
@@ -9656,7 +9688,7 @@
       <c r="I721" s="3"/>
       <c r="J721" s="3"/>
     </row>
-    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A722" s="14"/>
       <c r="B722" s="9"/>
       <c r="C722" s="9"/>
@@ -9668,7 +9700,7 @@
       <c r="I722" s="3"/>
       <c r="J722" s="3"/>
     </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A723" s="14"/>
       <c r="B723" s="9"/>
       <c r="C723" s="9"/>
@@ -9680,7 +9712,7 @@
       <c r="I723" s="3"/>
       <c r="J723" s="3"/>
     </row>
-    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A724" s="14"/>
       <c r="B724" s="9"/>
       <c r="C724" s="9"/>
@@ -9692,7 +9724,7 @@
       <c r="I724" s="3"/>
       <c r="J724" s="3"/>
     </row>
-    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A725" s="14"/>
       <c r="B725" s="9"/>
       <c r="C725" s="9"/>
@@ -9704,7 +9736,7 @@
       <c r="I725" s="3"/>
       <c r="J725" s="3"/>
     </row>
-    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A726" s="14"/>
       <c r="B726" s="9"/>
       <c r="C726" s="9"/>
@@ -9716,7 +9748,7 @@
       <c r="I726" s="3"/>
       <c r="J726" s="3"/>
     </row>
-    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A727" s="14"/>
       <c r="B727" s="9"/>
       <c r="C727" s="9"/>
@@ -9728,7 +9760,7 @@
       <c r="I727" s="3"/>
       <c r="J727" s="3"/>
     </row>
-    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A728" s="14"/>
       <c r="B728" s="9"/>
       <c r="C728" s="9"/>
@@ -9740,7 +9772,7 @@
       <c r="I728" s="3"/>
       <c r="J728" s="3"/>
     </row>
-    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A729" s="14"/>
       <c r="B729" s="9"/>
       <c r="C729" s="9"/>
@@ -9752,7 +9784,7 @@
       <c r="I729" s="3"/>
       <c r="J729" s="3"/>
     </row>
-    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A730" s="14"/>
       <c r="B730" s="9"/>
       <c r="C730" s="9"/>
@@ -9764,7 +9796,7 @@
       <c r="I730" s="3"/>
       <c r="J730" s="3"/>
     </row>
-    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A731" s="14"/>
       <c r="B731" s="9"/>
       <c r="C731" s="9"/>
@@ -9776,7 +9808,7 @@
       <c r="I731" s="3"/>
       <c r="J731" s="3"/>
     </row>
-    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A732" s="14"/>
       <c r="B732" s="9"/>
       <c r="C732" s="9"/>
@@ -9788,7 +9820,7 @@
       <c r="I732" s="3"/>
       <c r="J732" s="3"/>
     </row>
-    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A733" s="14"/>
       <c r="B733" s="9"/>
       <c r="C733" s="9"/>
@@ -9800,7 +9832,7 @@
       <c r="I733" s="3"/>
       <c r="J733" s="3"/>
     </row>
-    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A734" s="14"/>
       <c r="B734" s="9"/>
       <c r="C734" s="9"/>
@@ -9812,7 +9844,7 @@
       <c r="I734" s="3"/>
       <c r="J734" s="3"/>
     </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A735" s="14"/>
       <c r="B735" s="9"/>
       <c r="C735" s="9"/>
@@ -9824,7 +9856,7 @@
       <c r="I735" s="3"/>
       <c r="J735" s="3"/>
     </row>
-    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A736" s="14"/>
       <c r="B736" s="9"/>
       <c r="C736" s="9"/>
@@ -9836,7 +9868,7 @@
       <c r="I736" s="3"/>
       <c r="J736" s="3"/>
     </row>
-    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A737" s="14"/>
       <c r="B737" s="9"/>
       <c r="C737" s="9"/>
@@ -9848,7 +9880,7 @@
       <c r="I737" s="3"/>
       <c r="J737" s="3"/>
     </row>
-    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A738" s="14"/>
       <c r="B738" s="9"/>
       <c r="C738" s="9"/>
@@ -9860,7 +9892,7 @@
       <c r="I738" s="3"/>
       <c r="J738" s="3"/>
     </row>
-    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A739" s="14"/>
       <c r="B739" s="9"/>
       <c r="C739" s="9"/>
@@ -9872,7 +9904,7 @@
       <c r="I739" s="3"/>
       <c r="J739" s="3"/>
     </row>
-    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A740" s="14"/>
       <c r="B740" s="9"/>
       <c r="C740" s="9"/>
@@ -9884,7 +9916,7 @@
       <c r="I740" s="3"/>
       <c r="J740" s="3"/>
     </row>
-    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A741" s="14"/>
       <c r="B741" s="9"/>
       <c r="C741" s="9"/>
@@ -9896,7 +9928,7 @@
       <c r="I741" s="3"/>
       <c r="J741" s="3"/>
     </row>
-    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A742" s="14"/>
       <c r="B742" s="9"/>
       <c r="C742" s="9"/>
@@ -9908,7 +9940,7 @@
       <c r="I742" s="3"/>
       <c r="J742" s="3"/>
     </row>
-    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A743" s="14"/>
       <c r="B743" s="9"/>
       <c r="C743" s="9"/>
@@ -9920,7 +9952,7 @@
       <c r="I743" s="3"/>
       <c r="J743" s="3"/>
     </row>
-    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A744" s="14"/>
       <c r="B744" s="9"/>
       <c r="C744" s="9"/>
@@ -9932,7 +9964,7 @@
       <c r="I744" s="3"/>
       <c r="J744" s="3"/>
     </row>
-    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A745" s="14"/>
       <c r="B745" s="9"/>
       <c r="C745" s="9"/>
@@ -9944,7 +9976,7 @@
       <c r="I745" s="3"/>
       <c r="J745" s="3"/>
     </row>
-    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A746" s="14"/>
       <c r="B746" s="9"/>
       <c r="C746" s="9"/>
@@ -9956,7 +9988,7 @@
       <c r="I746" s="3"/>
       <c r="J746" s="3"/>
     </row>
-    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A747" s="14"/>
       <c r="B747" s="9"/>
       <c r="C747" s="9"/>
@@ -9968,7 +10000,7 @@
       <c r="I747" s="3"/>
       <c r="J747" s="3"/>
     </row>
-    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A748" s="14"/>
       <c r="B748" s="9"/>
       <c r="C748" s="9"/>
@@ -9980,7 +10012,7 @@
       <c r="I748" s="3"/>
       <c r="J748" s="3"/>
     </row>
-    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A749" s="14"/>
       <c r="B749" s="9"/>
       <c r="C749" s="9"/>
@@ -9992,7 +10024,7 @@
       <c r="I749" s="3"/>
       <c r="J749" s="3"/>
     </row>
-    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A750" s="14"/>
       <c r="B750" s="9"/>
       <c r="C750" s="9"/>
@@ -10004,7 +10036,7 @@
       <c r="I750" s="3"/>
       <c r="J750" s="3"/>
     </row>
-    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A751" s="14"/>
       <c r="B751" s="9"/>
       <c r="C751" s="9"/>
@@ -10016,7 +10048,7 @@
       <c r="I751" s="3"/>
       <c r="J751" s="3"/>
     </row>
-    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A752" s="14"/>
       <c r="B752" s="9"/>
       <c r="C752" s="9"/>
@@ -10028,7 +10060,7 @@
       <c r="I752" s="3"/>
       <c r="J752" s="3"/>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A753" s="14"/>
       <c r="B753" s="9"/>
       <c r="C753" s="9"/>
@@ -10040,7 +10072,7 @@
       <c r="I753" s="3"/>
       <c r="J753" s="3"/>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A754" s="14"/>
       <c r="B754" s="9"/>
       <c r="C754" s="9"/>
@@ -10052,7 +10084,7 @@
       <c r="I754" s="3"/>
       <c r="J754" s="3"/>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A755" s="14"/>
       <c r="B755" s="9"/>
       <c r="C755" s="9"/>
@@ -10064,7 +10096,7 @@
       <c r="I755" s="3"/>
       <c r="J755" s="3"/>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A756" s="14"/>
       <c r="B756" s="9"/>
       <c r="C756" s="9"/>
@@ -10076,7 +10108,7 @@
       <c r="I756" s="3"/>
       <c r="J756" s="3"/>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A757" s="14"/>
       <c r="B757" s="9"/>
       <c r="C757" s="9"/>
@@ -10088,7 +10120,7 @@
       <c r="I757" s="3"/>
       <c r="J757" s="3"/>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A758" s="14"/>
       <c r="B758" s="9"/>
       <c r="C758" s="9"/>
@@ -10100,7 +10132,7 @@
       <c r="I758" s="3"/>
       <c r="J758" s="3"/>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A759" s="14"/>
       <c r="B759" s="9"/>
       <c r="C759" s="9"/>
@@ -10112,7 +10144,7 @@
       <c r="I759" s="3"/>
       <c r="J759" s="3"/>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A760" s="14"/>
       <c r="B760" s="9"/>
       <c r="C760" s="9"/>
@@ -10124,7 +10156,7 @@
       <c r="I760" s="3"/>
       <c r="J760" s="3"/>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A761" s="14"/>
       <c r="B761" s="9"/>
       <c r="C761" s="9"/>
@@ -10136,7 +10168,7 @@
       <c r="I761" s="3"/>
       <c r="J761" s="3"/>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A762" s="14"/>
       <c r="B762" s="9"/>
       <c r="C762" s="9"/>
@@ -10148,7 +10180,7 @@
       <c r="I762" s="3"/>
       <c r="J762" s="3"/>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A763" s="14"/>
       <c r="B763" s="9"/>
       <c r="C763" s="9"/>
@@ -10160,7 +10192,7 @@
       <c r="I763" s="3"/>
       <c r="J763" s="3"/>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A764" s="14"/>
       <c r="B764" s="9"/>
       <c r="C764" s="9"/>
@@ -10172,7 +10204,7 @@
       <c r="I764" s="3"/>
       <c r="J764" s="3"/>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A765" s="14"/>
       <c r="B765" s="9"/>
       <c r="C765" s="9"/>
@@ -10184,7 +10216,7 @@
       <c r="I765" s="3"/>
       <c r="J765" s="3"/>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A766" s="14"/>
       <c r="B766" s="9"/>
       <c r="C766" s="9"/>
@@ -10196,7 +10228,7 @@
       <c r="I766" s="3"/>
       <c r="J766" s="3"/>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A767" s="14"/>
       <c r="B767" s="9"/>
       <c r="C767" s="9"/>
@@ -10208,7 +10240,7 @@
       <c r="I767" s="3"/>
       <c r="J767" s="3"/>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A768" s="14"/>
       <c r="B768" s="9"/>
       <c r="C768" s="9"/>
@@ -10220,7 +10252,7 @@
       <c r="I768" s="3"/>
       <c r="J768" s="3"/>
     </row>
-    <row r="769" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A769" s="14"/>
       <c r="B769" s="9"/>
       <c r="C769" s="9"/>
@@ -10232,7 +10264,7 @@
       <c r="I769" s="3"/>
       <c r="J769" s="3"/>
     </row>
-    <row r="770" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A770" s="14"/>
       <c r="B770" s="9"/>
       <c r="C770" s="9"/>
@@ -10244,7 +10276,7 @@
       <c r="I770" s="3"/>
       <c r="J770" s="3"/>
     </row>
-    <row r="771" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A771" s="14"/>
       <c r="B771" s="9"/>
       <c r="C771" s="9"/>
@@ -10256,7 +10288,7 @@
       <c r="I771" s="3"/>
       <c r="J771" s="3"/>
     </row>
-    <row r="772" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A772" s="14"/>
       <c r="B772" s="9"/>
       <c r="C772" s="9"/>
@@ -10268,7 +10300,7 @@
       <c r="I772" s="3"/>
       <c r="J772" s="3"/>
     </row>
-    <row r="773" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A773" s="14"/>
       <c r="B773" s="9"/>
       <c r="C773" s="9"/>
@@ -10280,7 +10312,7 @@
       <c r="I773" s="3"/>
       <c r="J773" s="3"/>
     </row>
-    <row r="774" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A774" s="14"/>
       <c r="B774" s="9"/>
       <c r="C774" s="9"/>
@@ -10292,7 +10324,7 @@
       <c r="I774" s="3"/>
       <c r="J774" s="3"/>
     </row>
-    <row r="775" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A775" s="14"/>
       <c r="B775" s="9"/>
       <c r="C775" s="9"/>
@@ -10304,7 +10336,7 @@
       <c r="I775" s="3"/>
       <c r="J775" s="3"/>
     </row>
-    <row r="776" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A776" s="14"/>
       <c r="B776" s="9"/>
       <c r="C776" s="9"/>
@@ -10316,7 +10348,7 @@
       <c r="I776" s="3"/>
       <c r="J776" s="3"/>
     </row>
-    <row r="777" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A777" s="14"/>
       <c r="B777" s="9"/>
       <c r="C777" s="9"/>
@@ -10328,7 +10360,7 @@
       <c r="I777" s="3"/>
       <c r="J777" s="3"/>
     </row>
-    <row r="778" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A778" s="14"/>
       <c r="B778" s="9"/>
       <c r="C778" s="9"/>
@@ -10340,7 +10372,7 @@
       <c r="I778" s="3"/>
       <c r="J778" s="3"/>
     </row>
-    <row r="779" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A779" s="14"/>
       <c r="B779" s="9"/>
       <c r="C779" s="9"/>
@@ -10352,7 +10384,7 @@
       <c r="I779" s="3"/>
       <c r="J779" s="3"/>
     </row>
-    <row r="780" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A780" s="14"/>
       <c r="B780" s="9"/>
       <c r="C780" s="9"/>
@@ -10364,7 +10396,7 @@
       <c r="I780" s="3"/>
       <c r="J780" s="3"/>
     </row>
-    <row r="781" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A781" s="14"/>
       <c r="B781" s="9"/>
       <c r="C781" s="9"/>
@@ -10376,7 +10408,7 @@
       <c r="I781" s="3"/>
       <c r="J781" s="3"/>
     </row>
-    <row r="782" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A782" s="14"/>
       <c r="B782" s="9"/>
       <c r="C782" s="9"/>
@@ -10388,7 +10420,7 @@
       <c r="I782" s="3"/>
       <c r="J782" s="3"/>
     </row>
-    <row r="783" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A783" s="14"/>
       <c r="B783" s="9"/>
       <c r="C783" s="9"/>
@@ -10400,7 +10432,7 @@
       <c r="I783" s="3"/>
       <c r="J783" s="3"/>
     </row>
-    <row r="784" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A784" s="14"/>
       <c r="B784" s="9"/>
       <c r="C784" s="9"/>
@@ -10412,7 +10444,7 @@
       <c r="I784" s="3"/>
       <c r="J784" s="3"/>
     </row>
-    <row r="785" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A785" s="14"/>
       <c r="B785" s="9"/>
       <c r="C785" s="9"/>
@@ -10424,7 +10456,7 @@
       <c r="I785" s="3"/>
       <c r="J785" s="3"/>
     </row>
-    <row r="786" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A786" s="14"/>
       <c r="B786" s="9"/>
       <c r="C786" s="9"/>
@@ -10436,7 +10468,7 @@
       <c r="I786" s="3"/>
       <c r="J786" s="3"/>
     </row>
-    <row r="787" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A787" s="14"/>
       <c r="B787" s="9"/>
       <c r="C787" s="9"/>
@@ -10448,7 +10480,7 @@
       <c r="I787" s="3"/>
       <c r="J787" s="3"/>
     </row>
-    <row r="788" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A788" s="14"/>
       <c r="B788" s="9"/>
       <c r="C788" s="9"/>
@@ -10460,7 +10492,7 @@
       <c r="I788" s="3"/>
       <c r="J788" s="3"/>
     </row>
-    <row r="789" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A789" s="14"/>
       <c r="B789" s="9"/>
       <c r="C789" s="9"/>
@@ -10472,7 +10504,7 @@
       <c r="I789" s="3"/>
       <c r="J789" s="3"/>
     </row>
-    <row r="790" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A790" s="14"/>
       <c r="B790" s="9"/>
       <c r="C790" s="9"/>
@@ -10484,7 +10516,7 @@
       <c r="I790" s="3"/>
       <c r="J790" s="3"/>
     </row>
-    <row r="791" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A791" s="14"/>
       <c r="B791" s="9"/>
       <c r="C791" s="9"/>
@@ -10496,7 +10528,7 @@
       <c r="I791" s="3"/>
       <c r="J791" s="3"/>
     </row>
-    <row r="792" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A792" s="14"/>
       <c r="B792" s="9"/>
       <c r="C792" s="9"/>
@@ -10508,7 +10540,7 @@
       <c r="I792" s="3"/>
       <c r="J792" s="3"/>
     </row>
-    <row r="793" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A793" s="14"/>
       <c r="B793" s="9"/>
       <c r="C793" s="9"/>
@@ -10520,7 +10552,7 @@
       <c r="I793" s="3"/>
       <c r="J793" s="3"/>
     </row>
-    <row r="794" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A794" s="14"/>
       <c r="B794" s="9"/>
       <c r="C794" s="9"/>
@@ -10532,7 +10564,7 @@
       <c r="I794" s="3"/>
       <c r="J794" s="3"/>
     </row>
-    <row r="795" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A795" s="14"/>
       <c r="B795" s="9"/>
       <c r="C795" s="9"/>
@@ -10544,7 +10576,7 @@
       <c r="I795" s="3"/>
       <c r="J795" s="3"/>
     </row>
-    <row r="796" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A796" s="14"/>
       <c r="B796" s="9"/>
       <c r="C796" s="9"/>
@@ -10556,7 +10588,7 @@
       <c r="I796" s="3"/>
       <c r="J796" s="3"/>
     </row>
-    <row r="797" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A797" s="14"/>
       <c r="B797" s="9"/>
       <c r="C797" s="9"/>
@@ -10568,7 +10600,7 @@
       <c r="I797" s="3"/>
       <c r="J797" s="3"/>
     </row>
-    <row r="798" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A798" s="14"/>
       <c r="B798" s="9"/>
       <c r="C798" s="9"/>
@@ -10580,7 +10612,7 @@
       <c r="I798" s="3"/>
       <c r="J798" s="3"/>
     </row>
-    <row r="799" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A799" s="14"/>
       <c r="B799" s="9"/>
       <c r="C799" s="9"/>
@@ -10592,7 +10624,7 @@
       <c r="I799" s="3"/>
       <c r="J799" s="3"/>
     </row>
-    <row r="800" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A800" s="14"/>
       <c r="B800" s="9"/>
       <c r="C800" s="9"/>
@@ -10604,7 +10636,7 @@
       <c r="I800" s="3"/>
       <c r="J800" s="3"/>
     </row>
-    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A801" s="14"/>
       <c r="B801" s="9"/>
       <c r="C801" s="9"/>
@@ -10616,7 +10648,7 @@
       <c r="I801" s="3"/>
       <c r="J801" s="3"/>
     </row>
-    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A802" s="14"/>
       <c r="B802" s="9"/>
       <c r="C802" s="9"/>
@@ -10628,7 +10660,7 @@
       <c r="I802" s="3"/>
       <c r="J802" s="3"/>
     </row>
-    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A803" s="14"/>
       <c r="B803" s="9"/>
       <c r="C803" s="9"/>
@@ -10640,7 +10672,7 @@
       <c r="I803" s="3"/>
       <c r="J803" s="3"/>
     </row>
-    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A804" s="14"/>
       <c r="B804" s="9"/>
       <c r="C804" s="9"/>
@@ -10652,7 +10684,7 @@
       <c r="I804" s="3"/>
       <c r="J804" s="3"/>
     </row>
-    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A805" s="14"/>
       <c r="B805" s="9"/>
       <c r="C805" s="9"/>
@@ -10664,7 +10696,7 @@
       <c r="I805" s="3"/>
       <c r="J805" s="3"/>
     </row>
-    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A806" s="14"/>
       <c r="B806" s="9"/>
       <c r="C806" s="9"/>
@@ -10676,7 +10708,7 @@
       <c r="I806" s="3"/>
       <c r="J806" s="3"/>
     </row>
-    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A807" s="14"/>
       <c r="B807" s="9"/>
       <c r="C807" s="9"/>
@@ -10688,7 +10720,7 @@
       <c r="I807" s="3"/>
       <c r="J807" s="3"/>
     </row>
-    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A808" s="14"/>
       <c r="B808" s="9"/>
       <c r="C808" s="9"/>
@@ -10700,7 +10732,7 @@
       <c r="I808" s="3"/>
       <c r="J808" s="3"/>
     </row>
-    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A809" s="14"/>
       <c r="B809" s="9"/>
       <c r="C809" s="9"/>
@@ -10712,7 +10744,7 @@
       <c r="I809" s="3"/>
       <c r="J809" s="3"/>
     </row>
-    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A810" s="14"/>
       <c r="B810" s="9"/>
       <c r="C810" s="9"/>
@@ -10724,7 +10756,7 @@
       <c r="I810" s="3"/>
       <c r="J810" s="3"/>
     </row>
-    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A811" s="14"/>
       <c r="B811" s="9"/>
       <c r="C811" s="9"/>
@@ -10736,7 +10768,7 @@
       <c r="I811" s="3"/>
       <c r="J811" s="3"/>
     </row>
-    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A812" s="14"/>
       <c r="B812" s="9"/>
       <c r="C812" s="9"/>
@@ -10748,7 +10780,7 @@
       <c r="I812" s="3"/>
       <c r="J812" s="3"/>
     </row>
-    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A813" s="14"/>
       <c r="B813" s="9"/>
       <c r="C813" s="9"/>
@@ -10760,7 +10792,7 @@
       <c r="I813" s="3"/>
       <c r="J813" s="3"/>
     </row>
-    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A814" s="14"/>
       <c r="B814" s="9"/>
       <c r="C814" s="9"/>
@@ -10772,7 +10804,7 @@
       <c r="I814" s="3"/>
       <c r="J814" s="3"/>
     </row>
-    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A815" s="14"/>
       <c r="B815" s="9"/>
       <c r="C815" s="9"/>
@@ -10784,7 +10816,7 @@
       <c r="I815" s="3"/>
       <c r="J815" s="3"/>
     </row>
-    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A816" s="14"/>
       <c r="B816" s="9"/>
       <c r="C816" s="9"/>
@@ -10796,7 +10828,7 @@
       <c r="I816" s="3"/>
       <c r="J816" s="3"/>
     </row>
-    <row r="817" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A817" s="14"/>
       <c r="B817" s="9"/>
       <c r="C817" s="9"/>
@@ -10808,7 +10840,7 @@
       <c r="I817" s="3"/>
       <c r="J817" s="3"/>
     </row>
-    <row r="818" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A818" s="14"/>
       <c r="B818" s="9"/>
       <c r="C818" s="9"/>
@@ -10820,7 +10852,7 @@
       <c r="I818" s="3"/>
       <c r="J818" s="3"/>
     </row>
-    <row r="819" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A819" s="14"/>
       <c r="B819" s="9"/>
       <c r="C819" s="9"/>
@@ -10832,7 +10864,7 @@
       <c r="I819" s="3"/>
       <c r="J819" s="3"/>
     </row>
-    <row r="820" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A820" s="14"/>
       <c r="B820" s="9"/>
       <c r="C820" s="9"/>
@@ -10844,7 +10876,7 @@
       <c r="I820" s="3"/>
       <c r="J820" s="3"/>
     </row>
-    <row r="821" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A821" s="14"/>
       <c r="B821" s="9"/>
       <c r="C821" s="9"/>
@@ -10856,7 +10888,7 @@
       <c r="I821" s="3"/>
       <c r="J821" s="3"/>
     </row>
-    <row r="822" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A822" s="14"/>
       <c r="B822" s="9"/>
       <c r="C822" s="9"/>
@@ -10868,7 +10900,7 @@
       <c r="I822" s="3"/>
       <c r="J822" s="3"/>
     </row>
-    <row r="823" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A823" s="14"/>
       <c r="B823" s="9"/>
       <c r="C823" s="9"/>
@@ -10880,7 +10912,7 @@
       <c r="I823" s="3"/>
       <c r="J823" s="3"/>
     </row>
-    <row r="824" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A824" s="14"/>
       <c r="B824" s="9"/>
       <c r="C824" s="9"/>
@@ -10892,7 +10924,7 @@
       <c r="I824" s="3"/>
       <c r="J824" s="3"/>
     </row>
-    <row r="825" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A825" s="14"/>
       <c r="B825" s="9"/>
       <c r="C825" s="9"/>
@@ -10904,7 +10936,7 @@
       <c r="I825" s="3"/>
       <c r="J825" s="3"/>
     </row>
-    <row r="826" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A826" s="14"/>
       <c r="B826" s="9"/>
       <c r="C826" s="9"/>
@@ -10916,7 +10948,7 @@
       <c r="I826" s="3"/>
       <c r="J826" s="3"/>
     </row>
-    <row r="827" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A827" s="14"/>
       <c r="B827" s="9"/>
       <c r="C827" s="9"/>
@@ -10928,7 +10960,7 @@
       <c r="I827" s="3"/>
       <c r="J827" s="3"/>
     </row>
-    <row r="828" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A828" s="14"/>
       <c r="B828" s="9"/>
       <c r="C828" s="9"/>
@@ -10940,7 +10972,7 @@
       <c r="I828" s="3"/>
       <c r="J828" s="3"/>
     </row>
-    <row r="829" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A829" s="14"/>
       <c r="B829" s="9"/>
       <c r="C829" s="9"/>
@@ -10952,7 +10984,7 @@
       <c r="I829" s="3"/>
       <c r="J829" s="3"/>
     </row>
-    <row r="830" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A830" s="14"/>
       <c r="B830" s="9"/>
       <c r="C830" s="9"/>
@@ -10964,7 +10996,7 @@
       <c r="I830" s="3"/>
       <c r="J830" s="3"/>
     </row>
-    <row r="831" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A831" s="14"/>
       <c r="B831" s="9"/>
       <c r="C831" s="9"/>
@@ -10976,7 +11008,7 @@
       <c r="I831" s="3"/>
       <c r="J831" s="3"/>
     </row>
-    <row r="832" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A832" s="14"/>
       <c r="B832" s="9"/>
       <c r="C832" s="9"/>
@@ -10988,7 +11020,7 @@
       <c r="I832" s="3"/>
       <c r="J832" s="3"/>
     </row>
-    <row r="833" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A833" s="14"/>
       <c r="B833" s="9"/>
       <c r="C833" s="9"/>
@@ -11000,7 +11032,7 @@
       <c r="I833" s="3"/>
       <c r="J833" s="3"/>
     </row>
-    <row r="834" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A834" s="14"/>
       <c r="B834" s="9"/>
       <c r="C834" s="9"/>
@@ -11012,7 +11044,7 @@
       <c r="I834" s="3"/>
       <c r="J834" s="3"/>
     </row>
-    <row r="835" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A835" s="14"/>
       <c r="B835" s="9"/>
       <c r="C835" s="9"/>
@@ -11024,7 +11056,7 @@
       <c r="I835" s="3"/>
       <c r="J835" s="3"/>
     </row>
-    <row r="836" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A836" s="14"/>
       <c r="B836" s="9"/>
       <c r="C836" s="9"/>
@@ -11036,7 +11068,7 @@
       <c r="I836" s="3"/>
       <c r="J836" s="3"/>
     </row>
-    <row r="837" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A837" s="14"/>
       <c r="B837" s="9"/>
       <c r="C837" s="9"/>
@@ -11048,7 +11080,7 @@
       <c r="I837" s="3"/>
       <c r="J837" s="3"/>
     </row>
-    <row r="838" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A838" s="14"/>
       <c r="B838" s="9"/>
       <c r="C838" s="9"/>
@@ -11060,7 +11092,7 @@
       <c r="I838" s="3"/>
       <c r="J838" s="3"/>
     </row>
-    <row r="839" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A839" s="14"/>
       <c r="B839" s="9"/>
       <c r="C839" s="9"/>
@@ -11072,7 +11104,7 @@
       <c r="I839" s="3"/>
       <c r="J839" s="3"/>
     </row>
-    <row r="840" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A840" s="14"/>
       <c r="B840" s="9"/>
       <c r="C840" s="9"/>
@@ -11084,7 +11116,7 @@
       <c r="I840" s="3"/>
       <c r="J840" s="3"/>
     </row>
-    <row r="841" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A841" s="14"/>
       <c r="B841" s="9"/>
       <c r="C841" s="9"/>
@@ -11096,7 +11128,7 @@
       <c r="I841" s="3"/>
       <c r="J841" s="3"/>
     </row>
-    <row r="842" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A842" s="14"/>
       <c r="B842" s="9"/>
       <c r="C842" s="9"/>
@@ -11108,7 +11140,7 @@
       <c r="I842" s="3"/>
       <c r="J842" s="3"/>
     </row>
-    <row r="843" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A843" s="14"/>
       <c r="B843" s="9"/>
       <c r="C843" s="9"/>
@@ -11120,7 +11152,7 @@
       <c r="I843" s="3"/>
       <c r="J843" s="3"/>
     </row>
-    <row r="844" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A844" s="14"/>
       <c r="B844" s="9"/>
       <c r="C844" s="9"/>
@@ -11132,7 +11164,7 @@
       <c r="I844" s="3"/>
       <c r="J844" s="3"/>
     </row>
-    <row r="845" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A845" s="14"/>
       <c r="B845" s="9"/>
       <c r="C845" s="9"/>
@@ -11144,7 +11176,7 @@
       <c r="I845" s="3"/>
       <c r="J845" s="3"/>
     </row>
-    <row r="846" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A846" s="14"/>
       <c r="B846" s="9"/>
       <c r="C846" s="9"/>
@@ -11156,7 +11188,7 @@
       <c r="I846" s="3"/>
       <c r="J846" s="3"/>
     </row>
-    <row r="847" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A847" s="14"/>
       <c r="B847" s="9"/>
       <c r="C847" s="9"/>
@@ -11168,7 +11200,7 @@
       <c r="I847" s="3"/>
       <c r="J847" s="3"/>
     </row>
-    <row r="848" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A848" s="14"/>
       <c r="B848" s="9"/>
       <c r="C848" s="9"/>
@@ -11180,7 +11212,7 @@
       <c r="I848" s="3"/>
       <c r="J848" s="3"/>
     </row>
-    <row r="849" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A849" s="14"/>
       <c r="B849" s="9"/>
       <c r="C849" s="9"/>
@@ -11192,7 +11224,7 @@
       <c r="I849" s="3"/>
       <c r="J849" s="3"/>
     </row>
-    <row r="850" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A850" s="14"/>
       <c r="B850" s="9"/>
       <c r="C850" s="9"/>
@@ -11204,7 +11236,7 @@
       <c r="I850" s="3"/>
       <c r="J850" s="3"/>
     </row>
-    <row r="851" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A851" s="14"/>
       <c r="B851" s="9"/>
       <c r="C851" s="9"/>
@@ -11216,7 +11248,7 @@
       <c r="I851" s="3"/>
       <c r="J851" s="3"/>
     </row>
-    <row r="852" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A852" s="14"/>
       <c r="B852" s="9"/>
       <c r="C852" s="9"/>
@@ -11228,7 +11260,7 @@
       <c r="I852" s="3"/>
       <c r="J852" s="3"/>
     </row>
-    <row r="853" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A853" s="14"/>
       <c r="B853" s="9"/>
       <c r="C853" s="9"/>
@@ -11240,7 +11272,7 @@
       <c r="I853" s="3"/>
       <c r="J853" s="3"/>
     </row>
-    <row r="854" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A854" s="14"/>
       <c r="B854" s="9"/>
       <c r="C854" s="9"/>
@@ -11252,7 +11284,7 @@
       <c r="I854" s="3"/>
       <c r="J854" s="3"/>
     </row>
-    <row r="855" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A855" s="14"/>
       <c r="B855" s="9"/>
       <c r="C855" s="9"/>
@@ -11264,7 +11296,7 @@
       <c r="I855" s="3"/>
       <c r="J855" s="3"/>
     </row>
-    <row r="856" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A856" s="14"/>
       <c r="B856" s="9"/>
       <c r="C856" s="9"/>
@@ -11276,7 +11308,7 @@
       <c r="I856" s="3"/>
       <c r="J856" s="3"/>
     </row>
-    <row r="857" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A857" s="14"/>
       <c r="B857" s="9"/>
       <c r="C857" s="9"/>
@@ -11288,7 +11320,7 @@
       <c r="I857" s="3"/>
       <c r="J857" s="3"/>
     </row>
-    <row r="858" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A858" s="14"/>
       <c r="B858" s="9"/>
       <c r="C858" s="9"/>
@@ -11300,7 +11332,7 @@
       <c r="I858" s="3"/>
       <c r="J858" s="3"/>
     </row>
-    <row r="859" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A859" s="14"/>
       <c r="B859" s="9"/>
       <c r="C859" s="9"/>
@@ -11312,7 +11344,7 @@
       <c r="I859" s="3"/>
       <c r="J859" s="3"/>
     </row>
-    <row r="860" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A860" s="14"/>
       <c r="B860" s="9"/>
       <c r="C860" s="9"/>
@@ -11324,7 +11356,7 @@
       <c r="I860" s="3"/>
       <c r="J860" s="3"/>
     </row>
-    <row r="861" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A861" s="14"/>
       <c r="B861" s="9"/>
       <c r="C861" s="9"/>
@@ -11336,7 +11368,7 @@
       <c r="I861" s="3"/>
       <c r="J861" s="3"/>
     </row>
-    <row r="862" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A862" s="14"/>
       <c r="B862" s="9"/>
       <c r="C862" s="9"/>
@@ -11348,7 +11380,7 @@
       <c r="I862" s="3"/>
       <c r="J862" s="3"/>
     </row>
-    <row r="863" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A863" s="14"/>
       <c r="B863" s="9"/>
       <c r="C863" s="9"/>
@@ -11360,7 +11392,7 @@
       <c r="I863" s="3"/>
       <c r="J863" s="3"/>
     </row>
-    <row r="864" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A864" s="14"/>
       <c r="B864" s="9"/>
       <c r="C864" s="9"/>
@@ -11372,7 +11404,7 @@
       <c r="I864" s="3"/>
       <c r="J864" s="3"/>
     </row>
-    <row r="865" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A865" s="14"/>
       <c r="B865" s="9"/>
       <c r="C865" s="9"/>
@@ -11384,7 +11416,7 @@
       <c r="I865" s="3"/>
       <c r="J865" s="3"/>
     </row>
-    <row r="866" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A866" s="14"/>
       <c r="B866" s="9"/>
       <c r="C866" s="9"/>
@@ -11396,7 +11428,7 @@
       <c r="I866" s="3"/>
       <c r="J866" s="3"/>
     </row>
-    <row r="867" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A867" s="14"/>
       <c r="B867" s="9"/>
       <c r="C867" s="9"/>
@@ -11408,7 +11440,7 @@
       <c r="I867" s="3"/>
       <c r="J867" s="3"/>
     </row>
-    <row r="868" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A868" s="14"/>
       <c r="B868" s="9"/>
       <c r="C868" s="9"/>
@@ -11420,7 +11452,7 @@
       <c r="I868" s="3"/>
       <c r="J868" s="3"/>
     </row>
-    <row r="869" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A869" s="14"/>
       <c r="B869" s="9"/>
       <c r="C869" s="9"/>
@@ -11432,7 +11464,7 @@
       <c r="I869" s="3"/>
       <c r="J869" s="3"/>
     </row>
-    <row r="870" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A870" s="14"/>
       <c r="B870" s="9"/>
       <c r="C870" s="9"/>
@@ -11444,7 +11476,7 @@
       <c r="I870" s="3"/>
       <c r="J870" s="3"/>
     </row>
-    <row r="871" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A871" s="14"/>
       <c r="B871" s="9"/>
       <c r="C871" s="9"/>
@@ -11456,7 +11488,7 @@
       <c r="I871" s="3"/>
       <c r="J871" s="3"/>
     </row>
-    <row r="872" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A872" s="14"/>
       <c r="B872" s="9"/>
       <c r="C872" s="9"/>
@@ -11468,7 +11500,7 @@
       <c r="I872" s="3"/>
       <c r="J872" s="3"/>
     </row>
-    <row r="873" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A873" s="14"/>
       <c r="B873" s="9"/>
       <c r="C873" s="9"/>
@@ -11480,7 +11512,7 @@
       <c r="I873" s="3"/>
       <c r="J873" s="3"/>
     </row>
-    <row r="874" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A874" s="14"/>
       <c r="B874" s="9"/>
       <c r="C874" s="9"/>
@@ -11492,7 +11524,7 @@
       <c r="I874" s="3"/>
       <c r="J874" s="3"/>
     </row>
-    <row r="875" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A875" s="14"/>
       <c r="B875" s="9"/>
       <c r="C875" s="9"/>
@@ -11504,7 +11536,7 @@
       <c r="I875" s="3"/>
       <c r="J875" s="3"/>
     </row>
-    <row r="876" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A876" s="14"/>
       <c r="B876" s="9"/>
       <c r="C876" s="9"/>
@@ -11516,7 +11548,7 @@
       <c r="I876" s="3"/>
       <c r="J876" s="3"/>
     </row>
-    <row r="877" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A877" s="14"/>
       <c r="B877" s="9"/>
       <c r="C877" s="9"/>
@@ -11528,7 +11560,7 @@
       <c r="I877" s="3"/>
       <c r="J877" s="3"/>
     </row>
-    <row r="878" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A878" s="14"/>
       <c r="B878" s="9"/>
       <c r="C878" s="9"/>
@@ -11540,7 +11572,7 @@
       <c r="I878" s="3"/>
       <c r="J878" s="3"/>
     </row>
-    <row r="879" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A879" s="14"/>
       <c r="B879" s="9"/>
       <c r="C879" s="9"/>
@@ -11552,7 +11584,7 @@
       <c r="I879" s="3"/>
       <c r="J879" s="3"/>
     </row>
-    <row r="880" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A880" s="14"/>
       <c r="B880" s="9"/>
       <c r="C880" s="9"/>
@@ -11564,7 +11596,7 @@
       <c r="I880" s="3"/>
       <c r="J880" s="3"/>
     </row>
-    <row r="881" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A881" s="14"/>
       <c r="B881" s="9"/>
       <c r="C881" s="9"/>
@@ -11576,7 +11608,7 @@
       <c r="I881" s="3"/>
       <c r="J881" s="3"/>
     </row>
-    <row r="882" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A882" s="14"/>
       <c r="B882" s="9"/>
       <c r="C882" s="9"/>
@@ -11588,7 +11620,7 @@
       <c r="I882" s="3"/>
       <c r="J882" s="3"/>
     </row>
-    <row r="883" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A883" s="14"/>
       <c r="B883" s="9"/>
       <c r="C883" s="9"/>
@@ -11600,7 +11632,7 @@
       <c r="I883" s="3"/>
       <c r="J883" s="3"/>
     </row>
-    <row r="884" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A884" s="14"/>
       <c r="B884" s="9"/>
       <c r="C884" s="9"/>
@@ -11612,7 +11644,7 @@
       <c r="I884" s="3"/>
       <c r="J884" s="3"/>
     </row>
-    <row r="885" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A885" s="14"/>
       <c r="B885" s="9"/>
       <c r="C885" s="9"/>
@@ -11624,7 +11656,7 @@
       <c r="I885" s="3"/>
       <c r="J885" s="3"/>
     </row>
-    <row r="886" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A886" s="14"/>
       <c r="B886" s="9"/>
       <c r="C886" s="9"/>
@@ -11636,7 +11668,7 @@
       <c r="I886" s="3"/>
       <c r="J886" s="3"/>
     </row>
-    <row r="887" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A887" s="14"/>
       <c r="B887" s="9"/>
       <c r="C887" s="9"/>
@@ -11648,7 +11680,7 @@
       <c r="I887" s="3"/>
       <c r="J887" s="3"/>
     </row>
-    <row r="888" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A888" s="14"/>
       <c r="B888" s="9"/>
       <c r="C888" s="9"/>
@@ -11660,7 +11692,7 @@
       <c r="I888" s="3"/>
       <c r="J888" s="3"/>
     </row>
-    <row r="889" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A889" s="14"/>
       <c r="B889" s="9"/>
       <c r="C889" s="9"/>
@@ -11672,7 +11704,7 @@
       <c r="I889" s="3"/>
       <c r="J889" s="3"/>
     </row>
-    <row r="890" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A890" s="14"/>
       <c r="B890" s="9"/>
       <c r="C890" s="9"/>
@@ -11684,7 +11716,7 @@
       <c r="I890" s="3"/>
       <c r="J890" s="3"/>
     </row>
-    <row r="891" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A891" s="14"/>
       <c r="B891" s="9"/>
       <c r="C891" s="9"/>
@@ -11696,7 +11728,7 @@
       <c r="I891" s="3"/>
       <c r="J891" s="3"/>
     </row>
-    <row r="892" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A892" s="14"/>
       <c r="B892" s="9"/>
       <c r="C892" s="9"/>
@@ -11708,7 +11740,7 @@
       <c r="I892" s="3"/>
       <c r="J892" s="3"/>
     </row>
-    <row r="893" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A893" s="14"/>
       <c r="B893" s="9"/>
       <c r="C893" s="9"/>
@@ -11720,7 +11752,7 @@
       <c r="I893" s="3"/>
       <c r="J893" s="3"/>
     </row>
-    <row r="894" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A894" s="14"/>
       <c r="B894" s="9"/>
       <c r="C894" s="9"/>
@@ -11732,7 +11764,7 @@
       <c r="I894" s="3"/>
       <c r="J894" s="3"/>
     </row>
-    <row r="895" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A895" s="14"/>
       <c r="B895" s="9"/>
       <c r="C895" s="9"/>
@@ -11744,7 +11776,7 @@
       <c r="I895" s="3"/>
       <c r="J895" s="3"/>
     </row>
-    <row r="896" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A896" s="14"/>
       <c r="B896" s="9"/>
       <c r="C896" s="9"/>
@@ -11756,7 +11788,7 @@
       <c r="I896" s="3"/>
       <c r="J896" s="3"/>
     </row>
-    <row r="897" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A897" s="14"/>
       <c r="B897" s="9"/>
       <c r="C897" s="9"/>
@@ -11768,7 +11800,7 @@
       <c r="I897" s="3"/>
       <c r="J897" s="3"/>
     </row>
-    <row r="898" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A898" s="14"/>
       <c r="B898" s="9"/>
       <c r="C898" s="9"/>
@@ -11780,7 +11812,7 @@
       <c r="I898" s="3"/>
       <c r="J898" s="3"/>
     </row>
-    <row r="899" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A899" s="14"/>
       <c r="B899" s="9"/>
       <c r="C899" s="9"/>
@@ -11792,7 +11824,7 @@
       <c r="I899" s="3"/>
       <c r="J899" s="3"/>
     </row>
-    <row r="900" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A900" s="14"/>
       <c r="B900" s="9"/>
       <c r="C900" s="9"/>
@@ -11804,7 +11836,7 @@
       <c r="I900" s="3"/>
       <c r="J900" s="3"/>
     </row>
-    <row r="901" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A901" s="14"/>
       <c r="B901" s="9"/>
       <c r="C901" s="9"/>
@@ -11816,7 +11848,7 @@
       <c r="I901" s="3"/>
       <c r="J901" s="3"/>
     </row>
-    <row r="902" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A902" s="14"/>
       <c r="B902" s="9"/>
       <c r="C902" s="9"/>
@@ -11828,7 +11860,7 @@
       <c r="I902" s="3"/>
       <c r="J902" s="3"/>
     </row>
-    <row r="903" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A903" s="14"/>
       <c r="B903" s="9"/>
       <c r="C903" s="9"/>
@@ -11840,7 +11872,7 @@
       <c r="I903" s="3"/>
       <c r="J903" s="3"/>
     </row>
-    <row r="904" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A904" s="14"/>
       <c r="B904" s="9"/>
       <c r="C904" s="9"/>
@@ -11852,7 +11884,7 @@
       <c r="I904" s="3"/>
       <c r="J904" s="3"/>
     </row>
-    <row r="905" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A905" s="14"/>
       <c r="B905" s="9"/>
       <c r="C905" s="9"/>
@@ -11864,7 +11896,7 @@
       <c r="I905" s="3"/>
       <c r="J905" s="3"/>
     </row>
-    <row r="906" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A906" s="14"/>
       <c r="B906" s="9"/>
       <c r="C906" s="9"/>
@@ -11876,7 +11908,7 @@
       <c r="I906" s="3"/>
       <c r="J906" s="3"/>
     </row>
-    <row r="907" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A907" s="14"/>
       <c r="B907" s="9"/>
       <c r="C907" s="9"/>
@@ -11888,7 +11920,7 @@
       <c r="I907" s="3"/>
       <c r="J907" s="3"/>
     </row>
-    <row r="908" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A908" s="14"/>
       <c r="B908" s="9"/>
       <c r="C908" s="9"/>
@@ -11900,7 +11932,7 @@
       <c r="I908" s="3"/>
       <c r="J908" s="3"/>
     </row>
-    <row r="909" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A909" s="14"/>
       <c r="B909" s="9"/>
       <c r="C909" s="9"/>
@@ -11912,7 +11944,7 @@
       <c r="I909" s="3"/>
       <c r="J909" s="3"/>
     </row>
-    <row r="910" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A910" s="14"/>
       <c r="B910" s="9"/>
       <c r="C910" s="9"/>
@@ -11924,7 +11956,7 @@
       <c r="I910" s="3"/>
       <c r="J910" s="3"/>
     </row>
-    <row r="911" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A911" s="14"/>
       <c r="B911" s="9"/>
       <c r="C911" s="9"/>
@@ -11936,7 +11968,7 @@
       <c r="I911" s="3"/>
       <c r="J911" s="3"/>
     </row>
-    <row r="912" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A912" s="14"/>
       <c r="B912" s="9"/>
       <c r="C912" s="9"/>
@@ -11948,7 +11980,7 @@
       <c r="I912" s="3"/>
       <c r="J912" s="3"/>
     </row>
-    <row r="913" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A913" s="14"/>
       <c r="B913" s="9"/>
       <c r="C913" s="9"/>
@@ -11960,7 +11992,7 @@
       <c r="I913" s="3"/>
       <c r="J913" s="3"/>
     </row>
-    <row r="914" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A914" s="14"/>
       <c r="B914" s="9"/>
       <c r="C914" s="9"/>
@@ -11972,7 +12004,7 @@
       <c r="I914" s="3"/>
       <c r="J914" s="3"/>
     </row>
-    <row r="915" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A915" s="14"/>
       <c r="B915" s="9"/>
       <c r="C915" s="9"/>
@@ -11984,7 +12016,7 @@
       <c r="I915" s="3"/>
       <c r="J915" s="3"/>
     </row>
-    <row r="916" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A916" s="14"/>
       <c r="B916" s="9"/>
       <c r="C916" s="9"/>
@@ -11996,7 +12028,7 @@
       <c r="I916" s="3"/>
       <c r="J916" s="3"/>
     </row>
-    <row r="917" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A917" s="14"/>
       <c r="B917" s="9"/>
       <c r="C917" s="9"/>
@@ -12008,7 +12040,7 @@
       <c r="I917" s="3"/>
       <c r="J917" s="3"/>
     </row>
-    <row r="918" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A918" s="14"/>
       <c r="B918" s="9"/>
       <c r="C918" s="9"/>
@@ -12020,7 +12052,7 @@
       <c r="I918" s="3"/>
       <c r="J918" s="3"/>
     </row>
-    <row r="919" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A919" s="14"/>
       <c r="B919" s="9"/>
       <c r="C919" s="9"/>
@@ -12032,7 +12064,7 @@
       <c r="I919" s="3"/>
       <c r="J919" s="3"/>
     </row>
-    <row r="920" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A920" s="14"/>
       <c r="B920" s="9"/>
       <c r="C920" s="9"/>
@@ -12044,7 +12076,7 @@
       <c r="I920" s="3"/>
       <c r="J920" s="3"/>
     </row>
-    <row r="921" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A921" s="14"/>
       <c r="B921" s="9"/>
       <c r="C921" s="9"/>
@@ -12056,7 +12088,7 @@
       <c r="I921" s="3"/>
       <c r="J921" s="3"/>
     </row>
-    <row r="922" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A922" s="14"/>
       <c r="B922" s="9"/>
       <c r="C922" s="9"/>
@@ -12068,7 +12100,7 @@
       <c r="I922" s="3"/>
       <c r="J922" s="3"/>
     </row>
-    <row r="923" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A923" s="14"/>
       <c r="B923" s="9"/>
       <c r="C923" s="9"/>
@@ -12080,7 +12112,7 @@
       <c r="I923" s="3"/>
       <c r="J923" s="3"/>
     </row>
-    <row r="924" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A924" s="14"/>
       <c r="B924" s="9"/>
       <c r="C924" s="9"/>
@@ -12092,7 +12124,7 @@
       <c r="I924" s="3"/>
       <c r="J924" s="3"/>
     </row>
-    <row r="925" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A925" s="14"/>
       <c r="B925" s="9"/>
       <c r="C925" s="9"/>
@@ -12104,7 +12136,7 @@
       <c r="I925" s="3"/>
       <c r="J925" s="3"/>
     </row>
-    <row r="926" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A926" s="14"/>
       <c r="B926" s="9"/>
       <c r="C926" s="9"/>
@@ -12116,7 +12148,7 @@
       <c r="I926" s="3"/>
       <c r="J926" s="3"/>
     </row>
-    <row r="927" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A927" s="14"/>
       <c r="B927" s="9"/>
       <c r="C927" s="9"/>
@@ -12128,7 +12160,7 @@
       <c r="I927" s="3"/>
       <c r="J927" s="3"/>
     </row>
-    <row r="928" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A928" s="14"/>
       <c r="B928" s="9"/>
       <c r="C928" s="9"/>
@@ -12140,7 +12172,7 @@
       <c r="I928" s="3"/>
       <c r="J928" s="3"/>
     </row>
-    <row r="929" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A929" s="14"/>
       <c r="B929" s="9"/>
       <c r="C929" s="9"/>
@@ -12152,7 +12184,7 @@
       <c r="I929" s="3"/>
       <c r="J929" s="3"/>
     </row>
-    <row r="930" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A930" s="14"/>
       <c r="B930" s="9"/>
       <c r="C930" s="9"/>
@@ -12164,7 +12196,7 @@
       <c r="I930" s="3"/>
       <c r="J930" s="3"/>
     </row>
-    <row r="931" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A931" s="14"/>
       <c r="B931" s="9"/>
       <c r="C931" s="9"/>
@@ -12176,7 +12208,7 @@
       <c r="I931" s="3"/>
       <c r="J931" s="3"/>
     </row>
-    <row r="932" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A932" s="14"/>
       <c r="B932" s="9"/>
       <c r="C932" s="9"/>
@@ -12188,7 +12220,7 @@
       <c r="I932" s="3"/>
       <c r="J932" s="3"/>
     </row>
-    <row r="933" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A933" s="14"/>
       <c r="B933" s="9"/>
       <c r="C933" s="9"/>
@@ -12200,7 +12232,7 @@
       <c r="I933" s="3"/>
       <c r="J933" s="3"/>
     </row>
-    <row r="934" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A934" s="14"/>
       <c r="B934" s="9"/>
       <c r="C934" s="9"/>
@@ -12212,7 +12244,7 @@
       <c r="I934" s="3"/>
       <c r="J934" s="3"/>
     </row>
-    <row r="935" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A935" s="14"/>
       <c r="B935" s="9"/>
       <c r="C935" s="9"/>
@@ -12224,7 +12256,7 @@
       <c r="I935" s="3"/>
       <c r="J935" s="3"/>
     </row>
-    <row r="936" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A936" s="14"/>
       <c r="B936" s="9"/>
       <c r="C936" s="9"/>
@@ -12236,7 +12268,7 @@
       <c r="I936" s="3"/>
       <c r="J936" s="3"/>
     </row>
-    <row r="937" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A937" s="14"/>
       <c r="B937" s="9"/>
       <c r="C937" s="9"/>
@@ -12248,7 +12280,7 @@
       <c r="I937" s="3"/>
       <c r="J937" s="3"/>
     </row>
-    <row r="938" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A938" s="14"/>
       <c r="B938" s="9"/>
       <c r="C938" s="9"/>
@@ -12260,7 +12292,7 @@
       <c r="I938" s="3"/>
       <c r="J938" s="3"/>
     </row>
-    <row r="939" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A939" s="14"/>
       <c r="B939" s="9"/>
       <c r="C939" s="9"/>
@@ -12272,7 +12304,7 @@
       <c r="I939" s="3"/>
       <c r="J939" s="3"/>
     </row>
-    <row r="940" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A940" s="14"/>
       <c r="B940" s="9"/>
       <c r="C940" s="9"/>
@@ -12284,7 +12316,7 @@
       <c r="I940" s="3"/>
       <c r="J940" s="3"/>
     </row>
-    <row r="941" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A941" s="14"/>
       <c r="B941" s="9"/>
       <c r="C941" s="9"/>
@@ -12296,7 +12328,7 @@
       <c r="I941" s="3"/>
       <c r="J941" s="3"/>
     </row>
-    <row r="942" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A942" s="14"/>
       <c r="B942" s="9"/>
       <c r="C942" s="9"/>
@@ -12308,7 +12340,7 @@
       <c r="I942" s="3"/>
       <c r="J942" s="3"/>
     </row>
-    <row r="943" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A943" s="14"/>
       <c r="B943" s="9"/>
       <c r="C943" s="9"/>
@@ -12320,7 +12352,7 @@
       <c r="I943" s="3"/>
       <c r="J943" s="3"/>
     </row>
-    <row r="944" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A944" s="14"/>
       <c r="B944" s="9"/>
       <c r="C944" s="9"/>
@@ -12332,7 +12364,7 @@
       <c r="I944" s="3"/>
       <c r="J944" s="3"/>
     </row>
-    <row r="945" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A945" s="14"/>
       <c r="B945" s="9"/>
       <c r="C945" s="9"/>
@@ -12344,7 +12376,7 @@
       <c r="I945" s="3"/>
       <c r="J945" s="3"/>
     </row>
-    <row r="946" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A946" s="14"/>
       <c r="B946" s="9"/>
       <c r="C946" s="9"/>
@@ -12356,7 +12388,7 @@
       <c r="I946" s="3"/>
       <c r="J946" s="3"/>
     </row>
-    <row r="947" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A947" s="14"/>
       <c r="B947" s="9"/>
       <c r="C947" s="9"/>
@@ -12368,7 +12400,7 @@
       <c r="I947" s="3"/>
       <c r="J947" s="3"/>
     </row>
-    <row r="948" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A948" s="14"/>
       <c r="B948" s="9"/>
       <c r="C948" s="9"/>
@@ -12380,7 +12412,7 @@
       <c r="I948" s="3"/>
       <c r="J948" s="3"/>
     </row>
-    <row r="949" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A949" s="14"/>
       <c r="B949" s="9"/>
       <c r="C949" s="9"/>
@@ -12392,7 +12424,7 @@
       <c r="I949" s="3"/>
       <c r="J949" s="3"/>
     </row>
-    <row r="950" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A950" s="14"/>
       <c r="B950" s="9"/>
       <c r="C950" s="9"/>
@@ -12404,7 +12436,7 @@
       <c r="I950" s="3"/>
       <c r="J950" s="3"/>
     </row>
-    <row r="951" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A951" s="14"/>
       <c r="B951" s="9"/>
       <c r="C951" s="9"/>
@@ -12416,7 +12448,7 @@
       <c r="I951" s="3"/>
       <c r="J951" s="3"/>
     </row>
-    <row r="952" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A952" s="14"/>
       <c r="B952" s="9"/>
       <c r="C952" s="9"/>
@@ -12428,7 +12460,7 @@
       <c r="I952" s="3"/>
       <c r="J952" s="3"/>
     </row>
-    <row r="953" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A953" s="14"/>
       <c r="B953" s="9"/>
       <c r="C953" s="9"/>
@@ -12440,7 +12472,7 @@
       <c r="I953" s="3"/>
       <c r="J953" s="3"/>
     </row>
-    <row r="954" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A954" s="14"/>
       <c r="B954" s="9"/>
       <c r="C954" s="9"/>
@@ -12452,7 +12484,7 @@
       <c r="I954" s="3"/>
       <c r="J954" s="3"/>
     </row>
-    <row r="955" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A955" s="14"/>
       <c r="B955" s="9"/>
       <c r="C955" s="9"/>
@@ -12464,7 +12496,7 @@
       <c r="I955" s="3"/>
       <c r="J955" s="3"/>
     </row>
-    <row r="956" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A956" s="14"/>
       <c r="B956" s="9"/>
       <c r="C956" s="9"/>
@@ -12476,7 +12508,7 @@
       <c r="I956" s="3"/>
       <c r="J956" s="3"/>
     </row>
-    <row r="957" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A957" s="14"/>
       <c r="B957" s="9"/>
       <c r="C957" s="9"/>
@@ -12488,7 +12520,7 @@
       <c r="I957" s="3"/>
       <c r="J957" s="3"/>
     </row>
-    <row r="958" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A958" s="14"/>
       <c r="B958" s="9"/>
       <c r="C958" s="9"/>
@@ -12500,7 +12532,7 @@
       <c r="I958" s="3"/>
       <c r="J958" s="3"/>
     </row>
-    <row r="959" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A959" s="14"/>
       <c r="B959" s="9"/>
       <c r="C959" s="9"/>
@@ -12512,7 +12544,7 @@
       <c r="I959" s="3"/>
       <c r="J959" s="3"/>
     </row>
-    <row r="960" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A960" s="14"/>
       <c r="B960" s="9"/>
       <c r="C960" s="9"/>
@@ -12524,7 +12556,7 @@
       <c r="I960" s="3"/>
       <c r="J960" s="3"/>
     </row>
-    <row r="961" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A961" s="14"/>
       <c r="B961" s="9"/>
       <c r="C961" s="9"/>
@@ -12536,6 +12568,18 @@
       <c r="I961" s="3"/>
       <c r="J961" s="3"/>
     </row>
+    <row r="962" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A962" s="14"/>
+      <c r="B962" s="9"/>
+      <c r="C962" s="9"/>
+      <c r="D962" s="5"/>
+      <c r="E962" s="5"/>
+      <c r="F962" s="3"/>
+      <c r="G962" s="5"/>
+      <c r="H962" s="5"/>
+      <c r="I962" s="3"/>
+      <c r="J962" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
